--- a/Config/PvpRelicConfig.xlsx
+++ b/Config/PvpRelicConfig.xlsx
@@ -283,7 +283,7 @@
     <t>Bandage</t>
   </si>
   <si>
-    <t>每回合开始时,恢复2点生命</t>
+    <t>每回合开始时,恢复20点生命</t>
   </si>
   <si>
     <t>114</t>
@@ -427,7 +427,7 @@
     <t>IronSandPalm</t>
   </si>
   <si>
-    <t>你造成的伤害+15点</t>
+    <t>你造成的伤害+150点</t>
   </si>
   <si>
     <t>126</t>
@@ -439,7 +439,7 @@
     <t>OldCottonJacket</t>
   </si>
   <si>
-    <t>每次受到的伤害降低3点</t>
+    <t>每次受到的伤害降低30点</t>
   </si>
   <si>
     <t>127</t>
@@ -616,7 +616,7 @@
     <t>20010|200101</t>
   </si>
   <si>
-    <t>获得60点生命上限,每回合结束后恢复2点血量</t>
+    <t>获得300点生命上限,每回合结束后恢复20点血量</t>
   </si>
   <si>
     <t>211</t>
@@ -769,7 +769,7 @@
     <t>20020</t>
   </si>
   <si>
-    <t>亮牌时,若战胜敌人,则永久+3生命上限</t>
+    <t>亮牌时,若战胜敌人,则永久+20生命上限</t>
   </si>
   <si>
     <t>221</t>
@@ -799,7 +799,7 @@
     <t>20022</t>
   </si>
   <si>
-    <t>每回合开始时,永久+1生命上限</t>
+    <t>每回合开始时,永久+10生命上限</t>
   </si>
   <si>
     <t>223</t>
@@ -844,7 +844,7 @@
     <t>20025</t>
   </si>
   <si>
-    <t>回合结束后,若你的血量低于50%,则恢复6点血量</t>
+    <t>回合结束后,若你的血量低于50%,则恢复50点血量</t>
   </si>
   <si>
     <t>226</t>
@@ -889,7 +889,7 @@
     <t>20029</t>
   </si>
   <si>
-    <t>每次比牌获胜后,恢复3点血量</t>
+    <t>每次比牌获胜后,恢复30点血量</t>
   </si>
   <si>
     <t>229</t>
@@ -994,7 +994,7 @@
     <t>20036|20037</t>
   </si>
   <si>
-    <t>结算时提供+8倍率,但回合结束后有18%的概率摧毁此圣物</t>
+    <t>结算时提供+2倍率,但回合结束后有18%的概率摧毁此圣物</t>
   </si>
   <si>
     <t>236</t>
@@ -1069,7 +1069,7 @@
     <t>Adrenaline</t>
   </si>
   <si>
-    <t>暴击时,回复8点生命</t>
+    <t>暴击时,回复40点生命</t>
   </si>
   <si>
     <t>242</t>
@@ -1204,7 +1204,7 @@
     <t>30004</t>
   </si>
   <si>
-    <t>每搓1次牌,结算时提供的倍率+1</t>
+    <t>每搓1次牌,结算时提供的倍率+0.5</t>
   </si>
   <si>
     <t>会员卡</t>
@@ -1228,7 +1228,7 @@
     <t>30007</t>
   </si>
   <si>
-    <t>亮出的每张8在结算时提供+100攻击力</t>
+    <t>亮出的每张8在结算时提供+25攻击力</t>
   </si>
   <si>
     <t>偶数韵律</t>
@@ -1408,7 +1408,7 @@
     <t>30028</t>
   </si>
   <si>
-    <t>使用后,玩家生命上限+80,并立即恢复80点血量</t>
+    <t>使用后,玩家生命上限+400,并立即恢复400点血量</t>
   </si>
   <si>
     <t>三花聚顶</t>
@@ -1477,7 +1477,7 @@
     <t>30036</t>
   </si>
   <si>
-    <t>比牌时留在手牌中的每一张K,都会提供+9倍率</t>
+    <t>比牌时留在手牌中的每一张K,都会提供+5倍率</t>
   </si>
   <si>
     <t>皇后领域</t>
@@ -1489,7 +1489,7 @@
     <t>30037</t>
   </si>
   <si>
-    <t>比牌时留在手牌中的每一张Q,都会提供+9倍率</t>
+    <t>比牌时留在手牌中的每一张Q,都会提供+5倍率</t>
   </si>
   <si>
     <t>妙手</t>
@@ -1522,7 +1522,7 @@
     <t>30042|30043</t>
   </si>
   <si>
-    <t>生命上限-100,攻击力+45</t>
+    <t>生命上限-400,攻击力+25</t>
   </si>
   <si>
     <t>雇佣兵</t>
@@ -1534,7 +1534,7 @@
     <t>30044|30045</t>
   </si>
   <si>
-    <t>获得60攻击力,每回合开始支付6金币,付不起则失效</t>
+    <t>获得25攻击力,每回合开始支付6金币,付不起则失效</t>
   </si>
   <si>
     <t>金钟罩</t>
@@ -1543,7 +1543,7 @@
     <t>GoldenBellShield</t>
   </si>
   <si>
-    <t>受到伤害时,消耗30金币抵挡该次伤害,金币不足则正常受伤</t>
+    <t>受到伤害时,消耗150金币抵挡该次伤害,金币不足则正常受伤</t>
   </si>
   <si>
     <t>悬赏令</t>
@@ -1618,7 +1618,7 @@
     <t>40002</t>
   </si>
   <si>
-    <t>获得240点生命上限</t>
+    <t>获得1200点生命上限</t>
   </si>
   <si>
     <t>403</t>
@@ -1648,7 +1648,7 @@
     <t>40005</t>
   </si>
   <si>
-    <t>结算时,若所有技能都无剩余使用次数,则提供+12倍率</t>
+    <t>结算时,若所有技能都无剩余使用次数,则提供+8倍率</t>
   </si>
   <si>
     <t>405</t>
@@ -1663,7 +1663,7 @@
     <t>40007</t>
   </si>
   <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+3倍率</t>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+2倍率</t>
   </si>
   <si>
     <t>406</t>
@@ -1693,7 +1693,7 @@
     <t>40009|400091</t>
   </si>
   <si>
-    <t>亮出的每张A在结算伤害时提供+66攻击力和+6倍率</t>
+    <t>亮出的每张A在结算伤害时提供+15攻击力和+3倍率</t>
   </si>
   <si>
     <t>408</t>
@@ -1768,7 +1768,7 @@
     <t>40014|400141|400142</t>
   </si>
   <si>
-    <t>亮出的每张7结算时必定提供+77攻击力和+7倍率</t>
+    <t>亮出的每张7结算时必定提供+20攻击力和+3倍率</t>
   </si>
   <si>
     <t>413</t>
@@ -1867,7 +1867,7 @@
     <t>DragonHeart</t>
   </si>
   <si>
-    <t>使用后,获得160点生命上限,并立即恢复160点血量</t>
+    <t>使用后,获得800点生命上限,并立即恢复800点血量</t>
   </si>
   <si>
     <t>421</t>
@@ -1891,7 +1891,7 @@
     <t>Flag</t>
   </si>
   <si>
-    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+12攻击力</t>
+    <t>在结算时,每剩余1个未使用的搓牌次数,就提供+8攻击力</t>
   </si>
   <si>
     <t>423</t>
@@ -1954,7 +1954,7 @@
     <t>40032</t>
   </si>
   <si>
-    <t>提供+100攻击力,但每次比牌后此效果会-5攻击力</t>
+    <t>提供+40攻击力,但每次比牌后此效果会-4攻击力</t>
   </si>
   <si>
     <t>427</t>
@@ -1999,7 +1999,7 @@
     <t>40035</t>
   </si>
   <si>
-    <t>在商店中每刷新1次,该圣物就会提供+1倍率</t>
+    <t>在商店中每刷新1次,该圣物就会提供+0.5倍率</t>
   </si>
   <si>
     <t>430</t>
@@ -2014,7 +2014,7 @@
     <t>40036</t>
   </si>
   <si>
-    <t>提供+20倍率,但每次比牌后此效果会-1倍率</t>
+    <t>提供+12倍率,但每次比牌后此效果会-1倍率</t>
   </si>
   <si>
     <t>431</t>
@@ -2729,14 +2729,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -2747,12 +2744,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3120,18 +3111,17 @@
   <cols>
     <col min="1" max="1" width="2.93333333333333" style="1" customWidth="1"/>
     <col min="2" max="2" width="4.125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.8" style="5" customWidth="1"/>
-    <col min="4" max="4" width="4.78333333333333" style="6" customWidth="1"/>
-    <col min="5" max="5" width="7.81666666666667" style="6" customWidth="1"/>
-    <col min="6" max="6" width="4.78333333333333" style="6" customWidth="1"/>
-    <col min="7" max="7" width="4.23333333333333" style="6" customWidth="1"/>
-    <col min="8" max="8" width="3.475" style="6" customWidth="1"/>
-    <col min="9" max="9" width="7.38333333333333" style="6" customWidth="1"/>
-    <col min="10" max="10" width="9.99166666666667" style="6" customWidth="1"/>
+    <col min="3" max="3" width="8.8" style="4" customWidth="1"/>
+    <col min="4" max="4" width="4.78333333333333" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.81666666666667" style="5" customWidth="1"/>
+    <col min="6" max="6" width="4.78333333333333" style="5" customWidth="1"/>
+    <col min="7" max="7" width="4.23333333333333" style="5" customWidth="1"/>
+    <col min="8" max="8" width="3.475" style="5" customWidth="1"/>
+    <col min="9" max="9" width="7.38333333333333" style="5" customWidth="1"/>
+    <col min="10" max="10" width="9.99166666666667" style="5" customWidth="1"/>
     <col min="11" max="11" width="33.0416666666667" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.70833333333333" style="6" customWidth="1"/>
-    <col min="14" max="16382" width="9" style="1" customWidth="1"/>
-    <col min="16383" max="16384" width="9" style="1"/>
+    <col min="13" max="13" width="7.70833333333333" style="5" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -3144,34 +3134,34 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3185,34 +3175,34 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3226,34 +3216,34 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>27</v>
       </c>
       <c r="L3" t="s">
         <v>28</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -3264,25 +3254,25 @@
       <c r="C5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>0.8</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>32</v>
       </c>
       <c r="F5" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="5">
         <v>45</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>22</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>10001</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>0</v>
       </c>
       <c r="L5" t="s">
@@ -3299,28 +3289,28 @@
       <c r="C6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>0.8</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>28</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>14</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>10002</v>
       </c>
-      <c r="J6" s="6">
+      <c r="J6" s="5">
         <v>101</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>0</v>
       </c>
       <c r="L6" t="s">
@@ -3337,28 +3327,28 @@
       <c r="C7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <v>0.8</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="5">
         <v>28</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>14</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>10003</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="5">
         <v>101</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>0</v>
       </c>
       <c r="L7" t="s">
@@ -3375,28 +3365,28 @@
       <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <v>0.8</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="5">
         <v>28</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>14</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>10004</v>
       </c>
-      <c r="J8" s="6">
+      <c r="J8" s="5">
         <v>101</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>0</v>
       </c>
       <c r="L8" t="s">
@@ -3413,28 +3403,28 @@
       <c r="C9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <v>0.8</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>28</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>14</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>10005</v>
       </c>
-      <c r="J9" s="6">
+      <c r="J9" s="5">
         <v>101</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>0</v>
       </c>
       <c r="L9" t="s">
@@ -3451,28 +3441,28 @@
       <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>0.8</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>28</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>14</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>10006</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="5">
         <v>102</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>0</v>
       </c>
       <c r="L10" t="s">
@@ -3489,28 +3479,28 @@
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <v>0.8</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="5">
         <v>22</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>11</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>10007</v>
       </c>
-      <c r="J11" s="6">
+      <c r="J11" s="5">
         <v>102</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>0</v>
       </c>
       <c r="L11" t="s">
@@ -3527,28 +3517,28 @@
       <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <v>0.8</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>35</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>17</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>10008</v>
       </c>
-      <c r="J12" s="6">
+      <c r="J12" s="5">
         <v>102</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>0</v>
       </c>
       <c r="L12" t="s">
@@ -3565,28 +3555,28 @@
       <c r="C13" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>0.8</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>16</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>8</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>10009</v>
       </c>
-      <c r="J13" s="6">
+      <c r="J13" s="5">
         <v>102</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>0</v>
       </c>
       <c r="L13" t="s">
@@ -3603,28 +3593,28 @@
       <c r="C14" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="5">
         <v>0.8</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="5">
         <v>16</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>8</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>10010</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="5">
         <v>102</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>0</v>
       </c>
       <c r="L14" t="s">
@@ -3641,28 +3631,28 @@
       <c r="C15" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="5">
         <v>0.8</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="5">
         <v>15</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>7</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>10011</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="5">
         <v>108</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>0</v>
       </c>
       <c r="L15" t="s">
@@ -3679,28 +3669,28 @@
       <c r="C16" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <v>0.8</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>30</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>15</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>10012</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="5">
         <v>107</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>0</v>
       </c>
       <c r="L16" t="s">
@@ -3717,28 +3707,28 @@
       <c r="C17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <v>0.8</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="5">
         <v>35</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>17</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>10013</v>
       </c>
-      <c r="J17" s="6">
+      <c r="J17" s="5">
         <v>108</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>0</v>
       </c>
       <c r="L17" t="s">
@@ -3755,28 +3745,28 @@
       <c r="C18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <v>0.8</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="5">
         <v>26</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>13</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <v>10014</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="5">
         <v>107</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>0</v>
       </c>
       <c r="L18" t="s">
@@ -3793,28 +3783,28 @@
       <c r="C19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>0.8</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>22</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>11</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>10015</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="5">
         <v>103</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>0</v>
       </c>
       <c r="L19" t="s">
@@ -3831,26 +3821,26 @@
       <c r="C20" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>0.8</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>28</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>14</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <v>10016</v>
       </c>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6">
+      <c r="J20" s="5"/>
+      <c r="K20" s="5">
         <v>0</v>
       </c>
       <c r="L20" t="s">
@@ -3867,25 +3857,25 @@
       <c r="C21" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <v>0.8</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="5">
         <v>20</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>10</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>10017</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>0</v>
       </c>
       <c r="L21" t="s">
@@ -3902,7 +3892,7 @@
       <c r="C22" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <v>0.8</v>
       </c>
       <c r="E22" t="s">
@@ -3911,17 +3901,17 @@
       <c r="F22" t="s">
         <v>102</v>
       </c>
-      <c r="G22" s="6">
+      <c r="G22" s="5">
         <v>25</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>12</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>10018</v>
       </c>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6">
+      <c r="J22" s="5"/>
+      <c r="K22" s="5">
         <v>1</v>
       </c>
       <c r="L22" t="s">
@@ -3938,7 +3928,7 @@
       <c r="C23" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <v>0.8</v>
       </c>
       <c r="E23" t="s">
@@ -3947,17 +3937,17 @@
       <c r="F23" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>25</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>12</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>10019</v>
       </c>
-      <c r="J23" s="6"/>
-      <c r="K23" s="6">
+      <c r="J23" s="5"/>
+      <c r="K23" s="5">
         <v>1</v>
       </c>
       <c r="L23" t="s">
@@ -3974,7 +3964,7 @@
       <c r="C24" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <v>0.8</v>
       </c>
       <c r="E24" t="s">
@@ -3983,19 +3973,19 @@
       <c r="F24" t="s">
         <v>110</v>
       </c>
-      <c r="G24" s="6">
+      <c r="G24" s="5">
         <v>30</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>15</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="5">
         <v>10020</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="5">
         <v>109</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>0</v>
       </c>
       <c r="L24" t="s">
@@ -4012,7 +4002,7 @@
       <c r="C25" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>0.8</v>
       </c>
       <c r="E25" t="s">
@@ -4021,17 +4011,17 @@
       <c r="F25" t="s">
         <v>114</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>35</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>17</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="5">
         <v>10021</v>
       </c>
-      <c r="J25" s="6"/>
-      <c r="K25" s="6">
+      <c r="J25" s="5"/>
+      <c r="K25" s="5">
         <v>2</v>
       </c>
       <c r="L25" t="s">
@@ -4041,262 +4031,262 @@
         <v>115</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" spans="2:13">
+    <row r="26" s="1" customFormat="1" spans="2:13">
       <c r="B26" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" t="s">
         <v>31</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="5">
         <v>0.8</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" t="s">
         <v>117</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G26" s="8">
+      <c r="G26" s="5">
         <v>25</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="5">
         <v>12</v>
       </c>
-      <c r="I26" s="8">
+      <c r="I26" s="5">
         <v>10022</v>
       </c>
-      <c r="K26" s="8">
-        <v>0</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M26" s="7" t="s">
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" t="s">
+        <v>34</v>
+      </c>
+      <c r="M26" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" spans="2:13">
+    <row r="27" s="1" customFormat="1" spans="2:13">
       <c r="B27" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="C27" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="5">
         <v>0.8</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="E27" t="s">
         <v>121</v>
       </c>
-      <c r="F27" s="7" t="s">
+      <c r="F27" t="s">
         <v>122</v>
       </c>
-      <c r="G27" s="8">
+      <c r="G27" s="5">
         <v>30</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="5">
         <v>15</v>
       </c>
-      <c r="I27" s="8">
+      <c r="I27" s="5">
         <v>10023</v>
       </c>
-      <c r="K27" s="8">
-        <v>0</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M27" s="7" t="s">
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
+      <c r="L27" t="s">
+        <v>34</v>
+      </c>
+      <c r="M27" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" spans="2:13">
+    <row r="28" s="1" customFormat="1" spans="2:13">
       <c r="B28" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" t="s">
         <v>31</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="5">
         <v>0.8</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" t="s">
         <v>125</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F28" t="s">
         <v>126</v>
       </c>
-      <c r="G28" s="8">
+      <c r="G28" s="5">
         <v>22</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="5">
         <v>11</v>
       </c>
-      <c r="I28" s="8">
+      <c r="I28" s="5">
         <v>10024</v>
       </c>
-      <c r="K28" s="8">
-        <v>0</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M28" s="7" t="s">
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
+      <c r="L28" t="s">
+        <v>34</v>
+      </c>
+      <c r="M28" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" spans="2:13">
+    <row r="29" s="1" customFormat="1" spans="2:13">
       <c r="B29" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" t="s">
         <v>31</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="5">
         <v>0.8</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" t="s">
         <v>129</v>
       </c>
-      <c r="F29" s="7" t="s">
+      <c r="F29" t="s">
         <v>130</v>
       </c>
-      <c r="G29" s="8">
+      <c r="G29" s="5">
         <v>20</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="5">
         <v>10</v>
       </c>
-      <c r="I29" s="8">
+      <c r="I29" s="5">
         <v>10025</v>
       </c>
-      <c r="K29" s="8">
-        <v>0</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M29" s="7" t="s">
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" t="s">
+        <v>34</v>
+      </c>
+      <c r="M29" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" spans="2:13">
+    <row r="30" s="1" customFormat="1" spans="2:13">
       <c r="B30" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="5">
         <v>0.8</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" t="s">
         <v>133</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" t="s">
         <v>134</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G30" s="5">
         <v>30</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="5">
         <v>15</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I30" s="5">
         <v>10026</v>
       </c>
-      <c r="K30" s="8">
-        <v>0</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M30" s="7" t="s">
+      <c r="K30" s="5">
+        <v>0</v>
+      </c>
+      <c r="L30" t="s">
+        <v>34</v>
+      </c>
+      <c r="M30" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" spans="2:13">
+    <row r="31" s="1" customFormat="1" spans="2:13">
       <c r="B31" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="5">
         <v>0.8</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" t="s">
         <v>137</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" t="s">
         <v>138</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="5">
         <v>25</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="5">
         <v>12</v>
       </c>
-      <c r="I31" s="8">
+      <c r="I31" s="5">
         <v>10027</v>
       </c>
-      <c r="K31" s="8">
-        <v>0</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M31" s="7" t="s">
+      <c r="K31" s="5">
+        <v>0</v>
+      </c>
+      <c r="L31" t="s">
+        <v>34</v>
+      </c>
+      <c r="M31" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" spans="2:13">
+    <row r="32" s="1" customFormat="1" spans="2:13">
       <c r="B32" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="5">
         <v>0.8</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" t="s">
         <v>141</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" t="s">
         <v>142</v>
       </c>
-      <c r="G32" s="8">
+      <c r="G32" s="5">
         <v>22</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="5">
         <v>11</v>
       </c>
-      <c r="I32" s="8">
+      <c r="I32" s="5">
         <v>10028</v>
       </c>
-      <c r="K32" s="8">
-        <v>0</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M32" s="7" t="s">
+      <c r="K32" s="5">
+        <v>0</v>
+      </c>
+      <c r="L32" t="s">
+        <v>34</v>
+      </c>
+      <c r="M32" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" spans="1:13">
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="5"/>
       <c r="L33"/>
-      <c r="M33" s="6"/>
+      <c r="M33" s="5"/>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:13">
       <c r="B34" s="1" t="s">
@@ -4305,13 +4295,13 @@
       <c r="C34" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D34" s="6">
+      <c r="D34" s="5">
         <v>0.4</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E34" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="F34" s="5" t="s">
         <v>147</v>
       </c>
       <c r="G34" s="1">
@@ -4323,10 +4313,10 @@
       <c r="I34" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="J34" s="6">
+      <c r="J34" s="5">
         <v>102</v>
       </c>
-      <c r="K34" s="6">
+      <c r="K34" s="5">
         <v>0</v>
       </c>
       <c r="L34" t="s">
@@ -4343,13 +4333,13 @@
       <c r="C35" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D35" s="6">
+      <c r="D35" s="5">
         <v>0.4</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="E35" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="F35" s="5" t="s">
         <v>152</v>
       </c>
       <c r="G35" s="1">
@@ -4361,10 +4351,10 @@
       <c r="I35" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="J35" s="6">
+      <c r="J35" s="5">
         <v>102</v>
       </c>
-      <c r="K35" s="6">
+      <c r="K35" s="5">
         <v>0</v>
       </c>
       <c r="L35" t="s">
@@ -4374,7 +4364,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="36" s="3" customFormat="1" spans="1:13">
+    <row r="36" s="2" customFormat="1" spans="1:13">
       <c r="A36"/>
       <c r="B36" s="1" t="s">
         <v>155</v>
@@ -4382,13 +4372,13 @@
       <c r="C36" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="5">
         <v>0.4</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="5" t="s">
         <v>157</v>
       </c>
       <c r="G36" s="1">
@@ -4400,10 +4390,10 @@
       <c r="I36" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="5">
         <v>102</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="5">
         <v>0</v>
       </c>
       <c r="L36" t="s">
@@ -4421,13 +4411,13 @@
       <c r="C37" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D37" s="6">
+      <c r="D37" s="5">
         <v>0.4</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="E37" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="F37" s="5" t="s">
         <v>162</v>
       </c>
       <c r="G37" s="1">
@@ -4439,10 +4429,10 @@
       <c r="I37" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="J37" s="6">
+      <c r="J37" s="5">
         <v>102</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="5">
         <v>0</v>
       </c>
       <c r="L37" t="s">
@@ -4452,7 +4442,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="38" s="3" customFormat="1" spans="1:13">
+    <row r="38" s="2" customFormat="1" spans="1:13">
       <c r="A38"/>
       <c r="B38" s="1" t="s">
         <v>165</v>
@@ -4460,13 +4450,13 @@
       <c r="C38" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D38" s="6">
+      <c r="D38" s="5">
         <v>0.4</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="E38" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F38" s="6" t="s">
+      <c r="F38" s="5" t="s">
         <v>167</v>
       </c>
       <c r="G38" s="1">
@@ -4478,8 +4468,8 @@
       <c r="I38" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6">
+      <c r="J38" s="5"/>
+      <c r="K38" s="5">
         <v>0</v>
       </c>
       <c r="L38" t="s">
@@ -4497,13 +4487,13 @@
       <c r="C39" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="5">
         <v>0.4</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="5" t="s">
         <v>172</v>
       </c>
       <c r="G39" s="1">
@@ -4515,8 +4505,8 @@
       <c r="I39" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6">
+      <c r="J39" s="5"/>
+      <c r="K39" s="5">
         <v>0</v>
       </c>
       <c r="L39" t="s">
@@ -4534,13 +4524,13 @@
       <c r="C40" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="5">
         <v>0.4</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="E40" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="F40" s="6" t="s">
+      <c r="F40" s="5" t="s">
         <v>177</v>
       </c>
       <c r="G40" s="1">
@@ -4552,8 +4542,8 @@
       <c r="I40" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="J40" s="6"/>
-      <c r="K40" s="6">
+      <c r="J40" s="5"/>
+      <c r="K40" s="5">
         <v>0</v>
       </c>
       <c r="L40" t="s">
@@ -4571,13 +4561,13 @@
       <c r="C41" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D41" s="6">
+      <c r="D41" s="5">
         <v>0.4</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="E41" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F41" s="6" t="s">
+      <c r="F41" s="5" t="s">
         <v>182</v>
       </c>
       <c r="G41" s="1">
@@ -4589,8 +4579,8 @@
       <c r="I41" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6">
+      <c r="J41" s="5"/>
+      <c r="K41" s="5">
         <v>0</v>
       </c>
       <c r="L41" t="s">
@@ -4608,13 +4598,13 @@
       <c r="C42" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D42" s="6">
+      <c r="D42" s="5">
         <v>0.4</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="5" t="s">
         <v>187</v>
       </c>
       <c r="G42" s="1">
@@ -4626,8 +4616,8 @@
       <c r="I42" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="J42" s="6"/>
-      <c r="K42" s="6">
+      <c r="J42" s="5"/>
+      <c r="K42" s="5">
         <v>0</v>
       </c>
       <c r="L42" t="s">
@@ -4638,35 +4628,35 @@
       </c>
     </row>
     <row r="43" s="1" customFormat="1" spans="1:13">
-      <c r="A43" s="9"/>
+      <c r="A43" s="6"/>
       <c r="B43" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D43" s="10">
+      <c r="D43" s="7">
         <v>0.4</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="G43" s="3">
+      <c r="G43" s="2">
         <v>140</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43" s="2">
         <v>70</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="I43" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="J43" s="10">
+      <c r="J43" s="7">
         <v>108</v>
       </c>
-      <c r="K43" s="10">
+      <c r="K43" s="7">
         <v>0</v>
       </c>
       <c r="L43" t="s">
@@ -4684,13 +4674,13 @@
       <c r="C44" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D44" s="6">
+      <c r="D44" s="5">
         <v>0.4</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="E44" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="F44" s="5" t="s">
         <v>197</v>
       </c>
       <c r="G44" s="1">
@@ -4702,53 +4692,53 @@
       <c r="I44" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6">
+      <c r="J44" s="5"/>
+      <c r="K44" s="5">
         <v>0</v>
       </c>
       <c r="L44" t="s">
         <v>34</v>
       </c>
-      <c r="M44" s="6" t="s">
+      <c r="M44" s="5" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="45" s="1" customFormat="1" spans="1:13">
-      <c r="A45" s="9"/>
+      <c r="A45" s="6"/>
       <c r="B45" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D45" s="10">
+      <c r="D45" s="7">
         <v>0.4</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="F45" s="10" t="s">
+      <c r="F45" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="G45" s="3">
+      <c r="G45" s="2">
         <v>135</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45" s="2">
         <v>67</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="J45" s="10">
+      <c r="J45" s="7">
         <v>105</v>
       </c>
-      <c r="K45" s="10">
+      <c r="K45" s="7">
         <v>0</v>
       </c>
       <c r="L45" t="s">
         <v>34</v>
       </c>
-      <c r="M45" s="9" t="s">
+      <c r="M45" s="6" t="s">
         <v>204</v>
       </c>
     </row>
@@ -4760,13 +4750,13 @@
       <c r="C46" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D46" s="6">
+      <c r="D46" s="5">
         <v>0.4</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="F46" s="6" t="s">
+      <c r="F46" s="5" t="s">
         <v>207</v>
       </c>
       <c r="G46" s="1">
@@ -4778,10 +4768,10 @@
       <c r="I46" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="J46" s="10" t="s">
+      <c r="J46" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="5">
         <v>0</v>
       </c>
       <c r="L46" t="s">
@@ -4799,13 +4789,13 @@
       <c r="C47" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D47" s="6">
+      <c r="D47" s="5">
         <v>0.4</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="E47" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="F47" s="6" t="s">
+      <c r="F47" s="5" t="s">
         <v>213</v>
       </c>
       <c r="G47" s="1" t="s">
@@ -4817,7 +4807,7 @@
       <c r="I47" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="5">
         <v>0</v>
       </c>
       <c r="L47" t="s">
@@ -4835,13 +4825,13 @@
       <c r="C48" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D48" s="6">
+      <c r="D48" s="5">
         <v>0.4</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="E48" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="F48" s="5" t="s">
         <v>218</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -4853,7 +4843,7 @@
       <c r="I48" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="5">
         <v>0</v>
       </c>
       <c r="L48" t="s">
@@ -4871,13 +4861,13 @@
       <c r="C49" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D49" s="6">
+      <c r="D49" s="5">
         <v>0.4</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="E49" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="F49" s="6" t="s">
+      <c r="F49" s="5" t="s">
         <v>223</v>
       </c>
       <c r="G49" s="1">
@@ -4889,7 +4879,7 @@
       <c r="I49" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="K49" s="6">
+      <c r="K49" s="5">
         <v>0</v>
       </c>
       <c r="L49" t="s">
@@ -4907,13 +4897,13 @@
       <c r="C50" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D50" s="6">
+      <c r="D50" s="5">
         <v>0.4</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="F50" s="6" t="s">
+      <c r="F50" s="5" t="s">
         <v>228</v>
       </c>
       <c r="G50" s="1">
@@ -4928,7 +4918,7 @@
       <c r="J50" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="5">
         <v>0</v>
       </c>
       <c r="L50" t="s">
@@ -4946,34 +4936,34 @@
       <c r="C51" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D51" s="6">
+      <c r="D51" s="5">
         <v>0.4</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="F51" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="G51" s="6">
+      <c r="G51" s="5">
         <v>85</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H51" s="5">
         <v>42</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J51" s="6">
+      <c r="J51" s="5">
         <v>109</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="5">
         <v>0</v>
       </c>
       <c r="L51" t="s">
         <v>34</v>
       </c>
-      <c r="M51" s="6" t="s">
+      <c r="M51" s="5" t="s">
         <v>235</v>
       </c>
     </row>
@@ -4985,26 +4975,26 @@
       <c r="C52" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D52" s="6">
+      <c r="D52" s="5">
         <v>0.4</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="F52" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G52" s="6">
+      <c r="G52" s="5">
         <v>75</v>
       </c>
-      <c r="H52" s="6">
+      <c r="H52" s="5">
         <v>37</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6">
+      <c r="J52" s="5"/>
+      <c r="K52" s="5">
         <v>0</v>
       </c>
       <c r="L52" t="s">
@@ -5022,28 +5012,28 @@
       <c r="C53" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D53" s="6">
+      <c r="D53" s="5">
         <v>0.4</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="F53" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G53" s="6">
+      <c r="G53" s="5">
         <v>75</v>
       </c>
-      <c r="H53" s="6">
+      <c r="H53" s="5">
         <v>37</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="J53" s="6">
+      <c r="J53" s="5">
         <v>108</v>
       </c>
-      <c r="K53" s="6">
+      <c r="K53" s="5">
         <v>0</v>
       </c>
       <c r="L53" t="s">
@@ -5061,28 +5051,28 @@
       <c r="C54" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D54" s="5">
         <v>0.4</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="F54" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="G54" s="6">
+      <c r="G54" s="5">
         <v>70</v>
       </c>
-      <c r="H54" s="6">
+      <c r="H54" s="5">
         <v>35</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="J54" s="6">
+      <c r="J54" s="5">
         <v>107</v>
       </c>
-      <c r="K54" s="6">
+      <c r="K54" s="5">
         <v>0</v>
       </c>
       <c r="L54" t="s">
@@ -5100,26 +5090,26 @@
       <c r="C55" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D55" s="5">
         <v>0.4</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="F55" s="6" t="s">
+      <c r="F55" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="G55" s="6">
+      <c r="G55" s="5">
         <v>75</v>
       </c>
-      <c r="H55" s="6">
+      <c r="H55" s="5">
         <v>37</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6">
+      <c r="J55" s="5"/>
+      <c r="K55" s="5">
         <v>0</v>
       </c>
       <c r="L55" t="s">
@@ -5136,32 +5126,32 @@
       <c r="C56" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D56" s="6">
+      <c r="D56" s="5">
         <v>0.4</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="F56" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="G56" s="6">
+      <c r="G56" s="5">
         <v>90</v>
       </c>
-      <c r="H56" s="6">
+      <c r="H56" s="5">
         <v>45</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6">
+      <c r="J56" s="5"/>
+      <c r="K56" s="5">
         <v>0</v>
       </c>
       <c r="L56" t="s">
         <v>34</v>
       </c>
-      <c r="M56" s="6" t="s">
+      <c r="M56" s="5" t="s">
         <v>260</v>
       </c>
     </row>
@@ -5173,34 +5163,34 @@
       <c r="C57" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D57" s="6">
+      <c r="D57" s="5">
         <v>0.4</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="F57" s="6" t="s">
+      <c r="F57" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="G57" s="6">
+      <c r="G57" s="5">
         <v>120</v>
       </c>
-      <c r="H57" s="6">
+      <c r="H57" s="5">
         <v>60</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="J57" s="6">
+      <c r="J57" s="5">
         <v>109</v>
       </c>
-      <c r="K57" s="6">
+      <c r="K57" s="5">
         <v>0</v>
       </c>
       <c r="L57" t="s">
         <v>34</v>
       </c>
-      <c r="M57" s="6" t="s">
+      <c r="M57" s="5" t="s">
         <v>265</v>
       </c>
     </row>
@@ -5212,28 +5202,28 @@
       <c r="C58" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="D58" s="6">
+      <c r="D58" s="5">
         <v>0.4</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="F58" s="6" t="s">
+      <c r="F58" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="G58" s="6">
+      <c r="G58" s="5">
         <v>109</v>
       </c>
-      <c r="H58" s="6">
+      <c r="H58" s="5">
         <v>55</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J58" s="6">
+      <c r="J58" s="5">
         <v>108</v>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="5">
         <v>0</v>
       </c>
       <c r="L58" t="s">
@@ -5250,7 +5240,7 @@
       <c r="C59" t="s">
         <v>145</v>
       </c>
-      <c r="D59" s="6">
+      <c r="D59" s="5">
         <v>0.4</v>
       </c>
       <c r="E59" t="s">
@@ -5259,17 +5249,17 @@
       <c r="F59" t="s">
         <v>273</v>
       </c>
-      <c r="G59" s="6">
+      <c r="G59" s="5">
         <v>90</v>
       </c>
-      <c r="H59" s="6">
+      <c r="H59" s="5">
         <v>45</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6">
+      <c r="J59" s="5"/>
+      <c r="K59" s="5">
         <v>1</v>
       </c>
       <c r="L59" t="s">
@@ -5286,7 +5276,7 @@
       <c r="C60" t="s">
         <v>145</v>
       </c>
-      <c r="D60" s="6">
+      <c r="D60" s="5">
         <v>0.4</v>
       </c>
       <c r="E60" t="s">
@@ -5295,17 +5285,17 @@
       <c r="F60" t="s">
         <v>278</v>
       </c>
-      <c r="G60" s="6">
+      <c r="G60" s="5">
         <v>145</v>
       </c>
-      <c r="H60" s="6">
+      <c r="H60" s="5">
         <v>72</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6">
+      <c r="J60" s="5"/>
+      <c r="K60" s="5">
         <v>1</v>
       </c>
       <c r="L60" t="s">
@@ -5322,7 +5312,7 @@
       <c r="C61" t="s">
         <v>145</v>
       </c>
-      <c r="D61" s="6">
+      <c r="D61" s="5">
         <v>0.4</v>
       </c>
       <c r="E61" t="s">
@@ -5331,19 +5321,19 @@
       <c r="F61" t="s">
         <v>283</v>
       </c>
-      <c r="G61" s="6">
+      <c r="G61" s="5">
         <v>95</v>
       </c>
-      <c r="H61" s="6">
+      <c r="H61" s="5">
         <v>47</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="J61" s="6">
+      <c r="J61" s="5">
         <v>108</v>
       </c>
-      <c r="K61" s="6">
+      <c r="K61" s="5">
         <v>0</v>
       </c>
       <c r="L61" t="s">
@@ -5360,7 +5350,7 @@
       <c r="C62" t="s">
         <v>145</v>
       </c>
-      <c r="D62" s="6">
+      <c r="D62" s="5">
         <v>0.4</v>
       </c>
       <c r="E62" t="s">
@@ -5369,17 +5359,17 @@
       <c r="F62" t="s">
         <v>288</v>
       </c>
-      <c r="G62" s="6">
+      <c r="G62" s="5">
         <v>109</v>
       </c>
-      <c r="H62" s="6">
+      <c r="H62" s="5">
         <v>55</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6">
+      <c r="J62" s="5"/>
+      <c r="K62" s="5">
         <v>1</v>
       </c>
       <c r="L62" t="s">
@@ -5396,7 +5386,7 @@
       <c r="C63" t="s">
         <v>145</v>
       </c>
-      <c r="D63" s="6">
+      <c r="D63" s="5">
         <v>0.4</v>
       </c>
       <c r="E63" t="s">
@@ -5405,17 +5395,17 @@
       <c r="F63" t="s">
         <v>293</v>
       </c>
-      <c r="G63" s="6">
+      <c r="G63" s="5">
         <v>160</v>
       </c>
-      <c r="H63" s="6">
+      <c r="H63" s="5">
         <v>80</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6">
+      <c r="J63" s="5"/>
+      <c r="K63" s="5">
         <v>2</v>
       </c>
       <c r="L63" t="s">
@@ -5432,7 +5422,7 @@
       <c r="C64" t="s">
         <v>145</v>
       </c>
-      <c r="D64" s="6">
+      <c r="D64" s="5">
         <v>0.4</v>
       </c>
       <c r="E64" t="s">
@@ -5441,23 +5431,23 @@
       <c r="F64" t="s">
         <v>298</v>
       </c>
-      <c r="G64" s="6">
+      <c r="G64" s="5">
         <v>160</v>
       </c>
-      <c r="H64" s="6">
+      <c r="H64" s="5">
         <v>80</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6">
+      <c r="J64" s="5"/>
+      <c r="K64" s="5">
         <v>2</v>
       </c>
       <c r="L64" t="s">
         <v>34</v>
       </c>
-      <c r="M64" s="6" t="s">
+      <c r="M64" s="5" t="s">
         <v>300</v>
       </c>
     </row>
@@ -5469,28 +5459,28 @@
       <c r="C65" t="s">
         <v>145</v>
       </c>
-      <c r="D65" s="6">
+      <c r="D65" s="5">
         <v>0.4</v>
       </c>
-      <c r="E65" s="6" t="s">
+      <c r="E65" s="5" t="s">
         <v>302</v>
       </c>
       <c r="F65" t="s">
         <v>303</v>
       </c>
-      <c r="G65" s="6">
+      <c r="G65" s="5">
         <v>80</v>
       </c>
-      <c r="H65" s="6">
+      <c r="H65" s="5">
         <v>40</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="J65" s="6">
+      <c r="J65" s="5">
         <v>104</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="5">
         <v>0</v>
       </c>
       <c r="L65" t="s">
@@ -5508,28 +5498,28 @@
       <c r="C66" t="s">
         <v>145</v>
       </c>
-      <c r="D66" s="6">
+      <c r="D66" s="5">
         <v>0.4</v>
       </c>
-      <c r="E66" s="6" t="s">
+      <c r="E66" s="5" t="s">
         <v>307</v>
       </c>
       <c r="F66" t="s">
         <v>308</v>
       </c>
-      <c r="G66" s="6">
+      <c r="G66" s="5">
         <v>80</v>
       </c>
-      <c r="H66" s="6">
+      <c r="H66" s="5">
         <v>40</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="J66" s="6">
+      <c r="J66" s="5">
         <v>104</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="5">
         <v>0</v>
       </c>
       <c r="L66" t="s">
@@ -5547,28 +5537,28 @@
       <c r="C67" t="s">
         <v>145</v>
       </c>
-      <c r="D67" s="6">
+      <c r="D67" s="5">
         <v>0.4</v>
       </c>
-      <c r="E67" s="6" t="s">
+      <c r="E67" s="5" t="s">
         <v>312</v>
       </c>
       <c r="F67" t="s">
         <v>313</v>
       </c>
-      <c r="G67" s="6">
+      <c r="G67" s="5">
         <v>80</v>
       </c>
-      <c r="H67" s="6">
+      <c r="H67" s="5">
         <v>40</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="J67" s="6">
+      <c r="J67" s="5">
         <v>104</v>
       </c>
-      <c r="K67" s="6">
+      <c r="K67" s="5">
         <v>0</v>
       </c>
       <c r="L67" t="s">
@@ -5578,542 +5568,542 @@
         <v>315</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" spans="1:13">
-      <c r="A68" s="7"/>
+    <row r="68" s="1" customFormat="1" spans="1:13">
+      <c r="A68"/>
       <c r="B68" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C68" s="7" t="s">
+      <c r="C68" t="s">
         <v>145</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="5">
         <v>0.4</v>
       </c>
-      <c r="E68" s="7" t="s">
+      <c r="E68" t="s">
         <v>317</v>
       </c>
-      <c r="F68" s="8" t="s">
+      <c r="F68" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="G68" s="8">
+      <c r="G68" s="5">
         <v>150</v>
       </c>
-      <c r="H68" s="8">
+      <c r="H68" s="5">
         <v>75</v>
       </c>
-      <c r="I68" s="8" t="s">
+      <c r="I68" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="J68" s="8"/>
-      <c r="K68" s="8">
-        <v>0</v>
-      </c>
-      <c r="L68" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M68" s="7" t="s">
+      <c r="J68" s="5"/>
+      <c r="K68" s="5">
+        <v>0</v>
+      </c>
+      <c r="L68" t="s">
+        <v>34</v>
+      </c>
+      <c r="M68" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="69" s="2" customFormat="1" spans="1:13">
-      <c r="A69" s="7"/>
+    <row r="69" s="1" customFormat="1" spans="1:13">
+      <c r="A69"/>
       <c r="B69" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="C69" s="7" t="s">
+      <c r="C69" t="s">
         <v>145</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="5">
         <v>0.4</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" t="s">
         <v>322</v>
       </c>
-      <c r="F69" s="8" t="s">
+      <c r="F69" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="G69" s="8">
+      <c r="G69" s="5">
         <v>109</v>
       </c>
-      <c r="H69" s="8">
+      <c r="H69" s="5">
         <v>55</v>
       </c>
-      <c r="I69" s="8" t="s">
+      <c r="I69" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="J69" s="8"/>
-      <c r="K69" s="8">
-        <v>0</v>
-      </c>
-      <c r="L69" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M69" s="7" t="s">
+      <c r="J69" s="5"/>
+      <c r="K69" s="5">
+        <v>0</v>
+      </c>
+      <c r="L69" t="s">
+        <v>34</v>
+      </c>
+      <c r="M69" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" spans="1:13">
-      <c r="A70" s="7"/>
+    <row r="70" s="1" customFormat="1" spans="1:13">
+      <c r="A70"/>
       <c r="B70" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="C70" s="7" t="s">
+      <c r="C70" t="s">
         <v>145</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="5">
         <v>0.4</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" t="s">
         <v>327</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" t="s">
         <v>328</v>
       </c>
-      <c r="G70" s="8">
+      <c r="G70" s="5">
         <v>120</v>
       </c>
-      <c r="H70" s="8">
+      <c r="H70" s="5">
         <v>60</v>
       </c>
-      <c r="I70" s="8">
+      <c r="I70" s="5">
         <v>20039</v>
       </c>
-      <c r="K70" s="8">
-        <v>0</v>
-      </c>
-      <c r="L70" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M70" s="7" t="s">
+      <c r="K70" s="5">
+        <v>0</v>
+      </c>
+      <c r="L70" t="s">
+        <v>34</v>
+      </c>
+      <c r="M70" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" spans="1:13">
-      <c r="A71" s="7"/>
+    <row r="71" s="1" customFormat="1" spans="1:13">
+      <c r="A71"/>
       <c r="B71" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="C71" s="7" t="s">
+      <c r="C71" t="s">
         <v>145</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="5">
         <v>0.4</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="E71" t="s">
         <v>331</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="F71" t="s">
         <v>332</v>
       </c>
-      <c r="G71" s="8">
+      <c r="G71" s="5">
         <v>110</v>
       </c>
-      <c r="H71" s="8">
+      <c r="H71" s="5">
         <v>55</v>
       </c>
-      <c r="I71" s="8">
+      <c r="I71" s="5">
         <v>20040</v>
       </c>
-      <c r="K71" s="8">
-        <v>0</v>
-      </c>
-      <c r="L71" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M71" s="7" t="s">
+      <c r="K71" s="5">
+        <v>0</v>
+      </c>
+      <c r="L71" t="s">
+        <v>34</v>
+      </c>
+      <c r="M71" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" spans="1:13">
-      <c r="A72" s="7"/>
+    <row r="72" s="1" customFormat="1" spans="1:13">
+      <c r="A72"/>
       <c r="B72" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" t="s">
         <v>145</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="5">
         <v>0.4</v>
       </c>
-      <c r="E72" s="7" t="s">
+      <c r="E72" t="s">
         <v>335</v>
       </c>
-      <c r="F72" s="7" t="s">
+      <c r="F72" t="s">
         <v>336</v>
       </c>
-      <c r="G72" s="8">
+      <c r="G72" s="5">
         <v>80</v>
       </c>
-      <c r="H72" s="8">
+      <c r="H72" s="5">
         <v>40</v>
       </c>
-      <c r="I72" s="8">
+      <c r="I72" s="5">
         <v>20041</v>
       </c>
-      <c r="K72" s="8">
-        <v>0</v>
-      </c>
-      <c r="L72" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M72" s="7" t="s">
+      <c r="K72" s="5">
+        <v>0</v>
+      </c>
+      <c r="L72" t="s">
+        <v>34</v>
+      </c>
+      <c r="M72" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="73" s="2" customFormat="1" spans="1:13">
-      <c r="A73" s="7"/>
+    <row r="73" s="1" customFormat="1" spans="1:13">
+      <c r="A73"/>
       <c r="B73" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C73" s="7" t="s">
+      <c r="C73" t="s">
         <v>145</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="5">
         <v>0.4</v>
       </c>
-      <c r="E73" s="7" t="s">
+      <c r="E73" t="s">
         <v>339</v>
       </c>
-      <c r="F73" s="7" t="s">
+      <c r="F73" t="s">
         <v>340</v>
       </c>
-      <c r="G73" s="8">
+      <c r="G73" s="5">
         <v>70</v>
       </c>
-      <c r="H73" s="8">
+      <c r="H73" s="5">
         <v>35</v>
       </c>
-      <c r="I73" s="8">
+      <c r="I73" s="5">
         <v>20042</v>
       </c>
-      <c r="K73" s="8">
-        <v>0</v>
-      </c>
-      <c r="L73" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M73" s="7" t="s">
+      <c r="K73" s="5">
+        <v>0</v>
+      </c>
+      <c r="L73" t="s">
+        <v>34</v>
+      </c>
+      <c r="M73" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="74" s="2" customFormat="1" spans="1:13">
-      <c r="A74" s="7"/>
+    <row r="74" s="1" customFormat="1" spans="1:13">
+      <c r="A74"/>
       <c r="B74" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="C74" s="7" t="s">
+      <c r="C74" t="s">
         <v>145</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="5">
         <v>0.4</v>
       </c>
-      <c r="E74" s="7" t="s">
+      <c r="E74" t="s">
         <v>343</v>
       </c>
-      <c r="F74" s="7" t="s">
+      <c r="F74" t="s">
         <v>344</v>
       </c>
-      <c r="G74" s="8">
+      <c r="G74" s="5">
         <v>95</v>
       </c>
-      <c r="H74" s="8">
+      <c r="H74" s="5">
         <v>47</v>
       </c>
-      <c r="I74" s="8">
+      <c r="I74" s="5">
         <v>20043</v>
       </c>
-      <c r="K74" s="8">
-        <v>0</v>
-      </c>
-      <c r="L74" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M74" s="7" t="s">
+      <c r="K74" s="5">
+        <v>0</v>
+      </c>
+      <c r="L74" t="s">
+        <v>34</v>
+      </c>
+      <c r="M74" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="75" s="2" customFormat="1" spans="1:13">
-      <c r="A75" s="7"/>
+    <row r="75" s="1" customFormat="1" spans="1:13">
+      <c r="A75"/>
       <c r="B75" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C75" s="7" t="s">
+      <c r="C75" t="s">
         <v>145</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="5">
         <v>0.4</v>
       </c>
-      <c r="E75" s="7" t="s">
+      <c r="E75" t="s">
         <v>347</v>
       </c>
-      <c r="F75" s="7" t="s">
+      <c r="F75" t="s">
         <v>348</v>
       </c>
-      <c r="G75" s="8">
+      <c r="G75" s="5">
         <v>120</v>
       </c>
-      <c r="H75" s="8">
+      <c r="H75" s="5">
         <v>60</v>
       </c>
-      <c r="I75" s="8">
+      <c r="I75" s="5">
         <v>20044</v>
       </c>
-      <c r="K75" s="8">
-        <v>0</v>
-      </c>
-      <c r="L75" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M75" s="7" t="s">
+      <c r="K75" s="5">
+        <v>0</v>
+      </c>
+      <c r="L75" t="s">
+        <v>34</v>
+      </c>
+      <c r="M75" t="s">
         <v>349</v>
       </c>
     </row>
-    <row r="76" s="4" customFormat="1" spans="1:13">
-      <c r="A76" s="11"/>
+    <row r="76" s="3" customFormat="1" spans="1:13">
+      <c r="A76" s="8"/>
       <c r="B76" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D76" s="12">
+      <c r="D76" s="9">
         <v>0.4</v>
       </c>
-      <c r="E76" s="11" t="s">
+      <c r="E76" s="8" t="s">
         <v>351</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="G76" s="12">
+      <c r="G76" s="9">
         <v>150</v>
       </c>
-      <c r="H76" s="12">
+      <c r="H76" s="9">
         <v>75</v>
       </c>
-      <c r="I76" s="12">
+      <c r="I76" s="9">
         <v>20045</v>
       </c>
-      <c r="K76" s="12">
-        <v>0</v>
-      </c>
-      <c r="L76" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M76" s="11" t="s">
+      <c r="K76" s="9">
+        <v>0</v>
+      </c>
+      <c r="L76" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M76" s="8" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="77" s="2" customFormat="1" spans="1:13">
-      <c r="A77" s="7"/>
+    <row r="77" s="1" customFormat="1" spans="1:13">
+      <c r="A77"/>
       <c r="B77" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="C77" s="7" t="s">
+      <c r="C77" t="s">
         <v>145</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="5">
         <v>0.4</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" t="s">
         <v>355</v>
       </c>
-      <c r="F77" s="7" t="s">
+      <c r="F77" t="s">
         <v>356</v>
       </c>
-      <c r="G77" s="8">
+      <c r="G77" s="5">
         <v>90</v>
       </c>
-      <c r="H77" s="8">
+      <c r="H77" s="5">
         <v>45</v>
       </c>
-      <c r="I77" s="8">
+      <c r="I77" s="5">
         <v>20046</v>
       </c>
-      <c r="K77" s="8">
-        <v>0</v>
-      </c>
-      <c r="L77" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M77" s="7" t="s">
+      <c r="K77" s="5">
+        <v>0</v>
+      </c>
+      <c r="L77" t="s">
+        <v>34</v>
+      </c>
+      <c r="M77" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="78" s="2" customFormat="1" spans="1:13">
-      <c r="A78" s="7"/>
+    <row r="78" s="1" customFormat="1" spans="1:13">
+      <c r="A78"/>
       <c r="B78" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C78" s="7" t="s">
+      <c r="C78" t="s">
         <v>145</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="5">
         <v>0.4</v>
       </c>
-      <c r="E78" s="7" t="s">
+      <c r="E78" t="s">
         <v>359</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="F78" t="s">
         <v>360</v>
       </c>
-      <c r="G78" s="8">
+      <c r="G78" s="5">
         <v>100</v>
       </c>
-      <c r="H78" s="8">
+      <c r="H78" s="5">
         <v>50</v>
       </c>
-      <c r="I78" s="8">
+      <c r="I78" s="5">
         <v>20047</v>
       </c>
-      <c r="K78" s="8">
-        <v>0</v>
-      </c>
-      <c r="L78" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M78" s="7" t="s">
+      <c r="K78" s="5">
+        <v>0</v>
+      </c>
+      <c r="L78" t="s">
+        <v>34</v>
+      </c>
+      <c r="M78" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="79" s="2" customFormat="1" spans="1:13">
-      <c r="A79" s="7"/>
+    <row r="79" s="1" customFormat="1" spans="1:13">
+      <c r="A79"/>
       <c r="B79" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C79" s="7" t="s">
+      <c r="C79" t="s">
         <v>145</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="5">
         <v>0.4</v>
       </c>
-      <c r="E79" s="7" t="s">
+      <c r="E79" t="s">
         <v>363</v>
       </c>
-      <c r="F79" s="7" t="s">
+      <c r="F79" t="s">
         <v>364</v>
       </c>
-      <c r="G79" s="8">
+      <c r="G79" s="5">
         <v>95</v>
       </c>
-      <c r="H79" s="8">
+      <c r="H79" s="5">
         <v>47</v>
       </c>
-      <c r="I79" s="8">
+      <c r="I79" s="5">
         <v>20048</v>
       </c>
-      <c r="K79" s="8">
-        <v>0</v>
-      </c>
-      <c r="L79" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M79" s="7" t="s">
+      <c r="K79" s="5">
+        <v>0</v>
+      </c>
+      <c r="L79" t="s">
+        <v>34</v>
+      </c>
+      <c r="M79" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="80" s="2" customFormat="1" spans="1:13">
-      <c r="A80" s="7"/>
+    <row r="80" s="1" customFormat="1" spans="1:13">
+      <c r="A80"/>
       <c r="B80" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="C80" s="7" t="s">
+      <c r="C80" t="s">
         <v>145</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="5">
         <v>0.4</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="E80" t="s">
         <v>367</v>
       </c>
-      <c r="F80" s="7" t="s">
+      <c r="F80" t="s">
         <v>368</v>
       </c>
-      <c r="G80" s="8">
+      <c r="G80" s="5">
         <v>85</v>
       </c>
-      <c r="H80" s="8">
+      <c r="H80" s="5">
         <v>42</v>
       </c>
-      <c r="I80" s="8">
+      <c r="I80" s="5">
         <v>20049</v>
       </c>
-      <c r="K80" s="8">
-        <v>0</v>
-      </c>
-      <c r="L80" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="M80" s="7" t="s">
+      <c r="K80" s="5">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>34</v>
+      </c>
+      <c r="M80" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="81" s="4" customFormat="1" spans="1:13">
-      <c r="A81" s="11"/>
+    <row r="81" s="3" customFormat="1" spans="1:13">
+      <c r="A81" s="8"/>
       <c r="B81" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="D81" s="12">
+      <c r="D81" s="9">
         <v>0.4</v>
       </c>
-      <c r="E81" s="11" t="s">
+      <c r="E81" s="8" t="s">
         <v>371</v>
       </c>
-      <c r="F81" s="11" t="s">
+      <c r="F81" s="8" t="s">
         <v>372</v>
       </c>
-      <c r="G81" s="12">
+      <c r="G81" s="9">
         <v>90</v>
       </c>
-      <c r="H81" s="12">
+      <c r="H81" s="9">
         <v>45</v>
       </c>
-      <c r="I81" s="12">
+      <c r="I81" s="9">
         <v>20050</v>
       </c>
-      <c r="K81" s="12">
-        <v>0</v>
-      </c>
-      <c r="L81" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M81" s="11" t="s">
+      <c r="K81" s="9">
+        <v>0</v>
+      </c>
+      <c r="L81" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M81" s="8" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="82" s="1" customFormat="1" spans="1:13">
       <c r="A82"/>
-      <c r="B82" s="6"/>
+      <c r="B82" s="5"/>
       <c r="C82" s="1"/>
-      <c r="D82" s="6"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="6"/>
-      <c r="K82" s="6"/>
+      <c r="J82" s="5"/>
+      <c r="K82" s="5"/>
       <c r="L82"/>
-      <c r="M82" s="6"/>
+      <c r="M82" s="5"/>
     </row>
     <row r="83" s="1" customFormat="1" spans="1:13">
       <c r="A83"/>
-      <c r="B83" s="6">
+      <c r="B83" s="5">
         <v>301</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D83" s="6">
+      <c r="D83" s="5">
         <v>0.2</v>
       </c>
-      <c r="E83" s="6" t="s">
+      <c r="E83" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="F83" s="5" t="s">
         <v>376</v>
       </c>
       <c r="G83" s="1">
@@ -6125,10 +6115,10 @@
       <c r="I83" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="J83" s="6">
+      <c r="J83" s="5">
         <v>101</v>
       </c>
-      <c r="K83" s="6">
+      <c r="K83" s="5">
         <v>0</v>
       </c>
       <c r="L83" t="s">
@@ -6140,19 +6130,19 @@
     </row>
     <row r="84" s="1" customFormat="1" spans="1:13">
       <c r="A84"/>
-      <c r="B84" s="6">
+      <c r="B84" s="5">
         <v>302</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D84" s="6">
+      <c r="D84" s="5">
         <v>0.2</v>
       </c>
-      <c r="E84" s="6" t="s">
+      <c r="E84" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="F84" s="6" t="s">
+      <c r="F84" s="5" t="s">
         <v>380</v>
       </c>
       <c r="G84" s="1">
@@ -6164,10 +6154,10 @@
       <c r="I84" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="J84" s="6">
+      <c r="J84" s="5">
         <v>104</v>
       </c>
-      <c r="K84" s="6">
+      <c r="K84" s="5">
         <v>0</v>
       </c>
       <c r="L84" t="s">
@@ -6179,19 +6169,19 @@
     </row>
     <row r="85" s="1" customFormat="1" spans="1:13">
       <c r="A85"/>
-      <c r="B85" s="6">
+      <c r="B85" s="5">
         <v>303</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D85" s="6">
+      <c r="D85" s="5">
         <v>0.2</v>
       </c>
-      <c r="E85" s="6" t="s">
+      <c r="E85" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="F85" s="6" t="s">
+      <c r="F85" s="5" t="s">
         <v>384</v>
       </c>
       <c r="G85" s="1">
@@ -6203,8 +6193,8 @@
       <c r="I85" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6">
+      <c r="J85" s="5"/>
+      <c r="K85" s="5">
         <v>0</v>
       </c>
       <c r="L85" t="s">
@@ -6216,19 +6206,19 @@
     </row>
     <row r="86" s="1" customFormat="1" spans="1:13">
       <c r="A86"/>
-      <c r="B86" s="6">
+      <c r="B86" s="5">
         <v>304</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D86" s="6">
+      <c r="D86" s="5">
         <v>0.2</v>
       </c>
-      <c r="E86" s="6" t="s">
+      <c r="E86" s="5" t="s">
         <v>387</v>
       </c>
-      <c r="F86" s="6" t="s">
+      <c r="F86" s="5" t="s">
         <v>388</v>
       </c>
       <c r="G86" s="1">
@@ -6240,8 +6230,8 @@
       <c r="I86" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="J86" s="6"/>
-      <c r="K86" s="6">
+      <c r="J86" s="5"/>
+      <c r="K86" s="5">
         <v>0</v>
       </c>
       <c r="L86" t="s">
@@ -6253,19 +6243,19 @@
     </row>
     <row r="87" s="1" customFormat="1" spans="1:13">
       <c r="A87"/>
-      <c r="B87" s="6">
+      <c r="B87" s="5">
         <v>305</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="5">
         <v>0.2</v>
       </c>
-      <c r="E87" s="6" t="s">
+      <c r="E87" s="5" t="s">
         <v>391</v>
       </c>
-      <c r="F87" s="6" t="s">
+      <c r="F87" s="5" t="s">
         <v>392</v>
       </c>
       <c r="G87" s="1">
@@ -6277,8 +6267,8 @@
       <c r="I87" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6">
+      <c r="J87" s="5"/>
+      <c r="K87" s="5">
         <v>0</v>
       </c>
       <c r="L87" t="s">
@@ -6289,19 +6279,19 @@
       </c>
     </row>
     <row r="88" s="1" customFormat="1" spans="1:13">
-      <c r="B88" s="6">
+      <c r="B88" s="5">
         <v>306</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D88" s="6">
+      <c r="D88" s="5">
         <v>0.2</v>
       </c>
-      <c r="E88" s="6" t="s">
+      <c r="E88" s="5" t="s">
         <v>395</v>
       </c>
-      <c r="F88" s="6" t="s">
+      <c r="F88" s="5" t="s">
         <v>396</v>
       </c>
       <c r="G88" s="1">
@@ -6313,7 +6303,7 @@
       <c r="I88" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="K88" s="6">
+      <c r="K88" s="5">
         <v>0</v>
       </c>
       <c r="L88" t="s">
@@ -6324,19 +6314,19 @@
       </c>
     </row>
     <row r="89" s="1" customFormat="1" spans="1:13">
-      <c r="B89" s="6">
+      <c r="B89" s="5">
         <v>307</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D89" s="6">
+      <c r="D89" s="5">
         <v>0.2</v>
       </c>
-      <c r="E89" s="6" t="s">
+      <c r="E89" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="F89" s="6" t="s">
+      <c r="F89" s="5" t="s">
         <v>400</v>
       </c>
       <c r="G89" s="1">
@@ -6348,10 +6338,10 @@
       <c r="I89" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="J89" s="6">
+      <c r="J89" s="5">
         <v>104</v>
       </c>
-      <c r="K89" s="6">
+      <c r="K89" s="5">
         <v>0</v>
       </c>
       <c r="L89" t="s">
@@ -6362,19 +6352,19 @@
       </c>
     </row>
     <row r="90" s="1" customFormat="1" spans="1:13">
-      <c r="B90" s="6">
+      <c r="B90" s="5">
         <v>308</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D90" s="6">
+      <c r="D90" s="5">
         <v>0.2</v>
       </c>
-      <c r="E90" s="6" t="s">
+      <c r="E90" s="5" t="s">
         <v>403</v>
       </c>
-      <c r="F90" s="6" t="s">
+      <c r="F90" s="5" t="s">
         <v>404</v>
       </c>
       <c r="G90" s="1">
@@ -6386,10 +6376,10 @@
       <c r="I90" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="J90" s="6">
+      <c r="J90" s="5">
         <v>104</v>
       </c>
-      <c r="K90" s="6">
+      <c r="K90" s="5">
         <v>0</v>
       </c>
       <c r="L90" t="s">
@@ -6400,19 +6390,19 @@
       </c>
     </row>
     <row r="91" s="1" customFormat="1" spans="1:13">
-      <c r="B91" s="6">
+      <c r="B91" s="5">
         <v>309</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D91" s="6">
+      <c r="D91" s="5">
         <v>0.2</v>
       </c>
-      <c r="E91" s="6" t="s">
+      <c r="E91" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="F91" s="6" t="s">
+      <c r="F91" s="5" t="s">
         <v>408</v>
       </c>
       <c r="G91" s="1">
@@ -6424,33 +6414,33 @@
       <c r="I91" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="J91" s="10">
+      <c r="J91" s="7">
         <v>105</v>
       </c>
-      <c r="K91" s="6">
+      <c r="K91" s="5">
         <v>0</v>
       </c>
       <c r="L91" t="s">
         <v>34</v>
       </c>
-      <c r="M91" s="6" t="s">
+      <c r="M91" s="5" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="92" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:13">
-      <c r="B92" s="6">
+      <c r="B92" s="5">
         <v>310</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D92" s="6">
+      <c r="D92" s="5">
         <v>0.2</v>
       </c>
-      <c r="E92" s="6" t="s">
+      <c r="E92" s="5" t="s">
         <v>411</v>
       </c>
-      <c r="F92" s="6" t="s">
+      <c r="F92" s="5" t="s">
         <v>412</v>
       </c>
       <c r="G92" s="1">
@@ -6462,7 +6452,7 @@
       <c r="I92" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="K92" s="6">
+      <c r="K92" s="5">
         <v>0</v>
       </c>
       <c r="L92" t="s">
@@ -6473,19 +6463,19 @@
       </c>
     </row>
     <row r="93" s="1" customFormat="1" spans="1:13">
-      <c r="B93" s="6">
+      <c r="B93" s="5">
         <v>311</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D93" s="6">
+      <c r="D93" s="5">
         <v>0.2</v>
       </c>
-      <c r="E93" s="6" t="s">
+      <c r="E93" s="5" t="s">
         <v>415</v>
       </c>
-      <c r="F93" s="6" t="s">
+      <c r="F93" s="5" t="s">
         <v>416</v>
       </c>
       <c r="G93" s="1">
@@ -6497,10 +6487,10 @@
       <c r="I93" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="J93" s="6">
+      <c r="J93" s="5">
         <v>107</v>
       </c>
-      <c r="K93" s="6">
+      <c r="K93" s="5">
         <v>0</v>
       </c>
       <c r="L93" t="s">
@@ -6511,32 +6501,32 @@
       </c>
     </row>
     <row r="94" s="1" customFormat="1" spans="1:13">
-      <c r="B94" s="6">
+      <c r="B94" s="5">
         <v>312</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D94" s="6">
+      <c r="D94" s="5">
         <v>0.2</v>
       </c>
-      <c r="E94" s="6" t="s">
+      <c r="E94" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="F94" s="6" t="s">
+      <c r="F94" s="5" t="s">
         <v>420</v>
       </c>
-      <c r="G94" s="6">
+      <c r="G94" s="5">
         <v>165</v>
       </c>
-      <c r="H94" s="6">
+      <c r="H94" s="5">
         <v>82</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6">
+      <c r="J94" s="5"/>
+      <c r="K94" s="5">
         <v>0</v>
       </c>
       <c r="L94" t="s">
@@ -6547,32 +6537,32 @@
       </c>
     </row>
     <row r="95" s="1" customFormat="1" spans="1:13">
-      <c r="B95" s="6">
+      <c r="B95" s="5">
         <v>313</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D95" s="6">
+      <c r="D95" s="5">
         <v>0.2</v>
       </c>
-      <c r="E95" s="6" t="s">
+      <c r="E95" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="F95" s="6" t="s">
+      <c r="F95" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="G95" s="6">
+      <c r="G95" s="5">
         <v>200</v>
       </c>
-      <c r="H95" s="6">
+      <c r="H95" s="5">
         <v>100</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="J95" s="6"/>
-      <c r="K95" s="6">
+      <c r="J95" s="5"/>
+      <c r="K95" s="5">
         <v>0</v>
       </c>
       <c r="L95" t="s">
@@ -6583,68 +6573,68 @@
       </c>
     </row>
     <row r="96" s="1" customFormat="1" spans="1:13">
-      <c r="B96" s="6">
+      <c r="B96" s="5">
         <v>314</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D96" s="6">
+      <c r="D96" s="5">
         <v>0.2</v>
       </c>
-      <c r="E96" s="6" t="s">
+      <c r="E96" s="5" t="s">
         <v>427</v>
       </c>
-      <c r="F96" s="6" t="s">
+      <c r="F96" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="G96" s="6">
+      <c r="G96" s="5">
         <v>220</v>
       </c>
-      <c r="H96" s="6">
+      <c r="H96" s="5">
         <v>109</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6">
+      <c r="J96" s="5"/>
+      <c r="K96" s="5">
         <v>0</v>
       </c>
       <c r="L96" t="s">
         <v>34</v>
       </c>
-      <c r="M96" s="6" t="s">
+      <c r="M96" s="5" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="1:13">
-      <c r="B97" s="6">
+      <c r="B97" s="5">
         <v>315</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D97" s="6">
+      <c r="D97" s="5">
         <v>0.2</v>
       </c>
-      <c r="E97" s="6" t="s">
+      <c r="E97" s="5" t="s">
         <v>431</v>
       </c>
-      <c r="F97" s="6" t="s">
+      <c r="F97" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="G97" s="6">
+      <c r="G97" s="5">
         <v>200</v>
       </c>
-      <c r="H97" s="6">
+      <c r="H97" s="5">
         <v>100</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="J97" s="6"/>
-      <c r="K97" s="6">
+      <c r="J97" s="5"/>
+      <c r="K97" s="5">
         <v>0</v>
       </c>
       <c r="L97" t="s">
@@ -6655,34 +6645,34 @@
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="1:13">
-      <c r="B98" s="6">
+      <c r="B98" s="5">
         <v>316</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D98" s="6">
+      <c r="D98" s="5">
         <v>0.2</v>
       </c>
-      <c r="E98" s="6" t="s">
+      <c r="E98" s="5" t="s">
         <v>435</v>
       </c>
-      <c r="F98" s="6" t="s">
+      <c r="F98" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="G98" s="6">
+      <c r="G98" s="5">
         <v>190</v>
       </c>
-      <c r="H98" s="6">
+      <c r="H98" s="5">
         <v>95</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="J98" s="6">
+      <c r="J98" s="5">
         <v>109</v>
       </c>
-      <c r="K98" s="6">
+      <c r="K98" s="5">
         <v>0</v>
       </c>
       <c r="L98" t="s">
@@ -6693,32 +6683,32 @@
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="1:13">
-      <c r="B99" s="6">
+      <c r="B99" s="5">
         <v>317</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D99" s="6">
+      <c r="D99" s="5">
         <v>0.2</v>
       </c>
-      <c r="E99" s="6" t="s">
+      <c r="E99" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="F99" s="6" t="s">
+      <c r="F99" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="G99" s="6">
+      <c r="G99" s="5">
         <v>190</v>
       </c>
-      <c r="H99" s="6">
+      <c r="H99" s="5">
         <v>95</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>441</v>
       </c>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6">
+      <c r="J99" s="5"/>
+      <c r="K99" s="5">
         <v>0</v>
       </c>
       <c r="L99" t="s">
@@ -6729,32 +6719,32 @@
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="1:13">
-      <c r="B100" s="6">
+      <c r="B100" s="5">
         <v>318</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D100" s="6">
+      <c r="D100" s="5">
         <v>0.2</v>
       </c>
-      <c r="E100" s="6" t="s">
+      <c r="E100" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="F100" s="6" t="s">
+      <c r="F100" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="G100" s="6">
+      <c r="G100" s="5">
         <v>210</v>
       </c>
-      <c r="H100" s="6">
+      <c r="H100" s="5">
         <v>105</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>445</v>
       </c>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6">
+      <c r="J100" s="5"/>
+      <c r="K100" s="5">
         <v>0</v>
       </c>
       <c r="L100" t="s">
@@ -6765,32 +6755,32 @@
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="1:13">
-      <c r="B101" s="6">
+      <c r="B101" s="5">
         <v>319</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="D101" s="6">
+      <c r="D101" s="5">
         <v>0.2</v>
       </c>
-      <c r="E101" s="6" t="s">
+      <c r="E101" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="F101" s="6" t="s">
+      <c r="F101" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="G101" s="6">
+      <c r="G101" s="5">
         <v>200</v>
       </c>
-      <c r="H101" s="6">
+      <c r="H101" s="5">
         <v>100</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6">
+      <c r="J101" s="5"/>
+      <c r="K101" s="5">
         <v>0</v>
       </c>
       <c r="L101" t="s">
@@ -6801,13 +6791,13 @@
       </c>
     </row>
     <row r="102" s="1" customFormat="1" spans="1:13">
-      <c r="B102" s="6">
+      <c r="B102" s="5">
         <v>320</v>
       </c>
       <c r="C102" t="s">
         <v>374</v>
       </c>
-      <c r="D102" s="6">
+      <c r="D102" s="5">
         <v>0.2</v>
       </c>
       <c r="E102" t="s">
@@ -6816,17 +6806,17 @@
       <c r="F102" t="s">
         <v>452</v>
       </c>
-      <c r="G102" s="6">
+      <c r="G102" s="5">
         <v>190</v>
       </c>
-      <c r="H102" s="6">
+      <c r="H102" s="5">
         <v>95</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="J102" s="6"/>
-      <c r="K102" s="6">
+      <c r="J102" s="5"/>
+      <c r="K102" s="5">
         <v>2</v>
       </c>
       <c r="L102" t="s">
@@ -6837,13 +6827,13 @@
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="1:13">
-      <c r="B103" s="6">
+      <c r="B103" s="5">
         <v>321</v>
       </c>
       <c r="C103" t="s">
         <v>374</v>
       </c>
-      <c r="D103" s="6">
+      <c r="D103" s="5">
         <v>0.2</v>
       </c>
       <c r="E103" t="s">
@@ -6852,17 +6842,17 @@
       <c r="F103" t="s">
         <v>456</v>
       </c>
-      <c r="G103" s="6">
+      <c r="G103" s="5">
         <v>200</v>
       </c>
-      <c r="H103" s="6">
+      <c r="H103" s="5">
         <v>100</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="J103" s="6"/>
-      <c r="K103" s="6">
+      <c r="J103" s="5"/>
+      <c r="K103" s="5">
         <v>1</v>
       </c>
       <c r="L103" t="s">
@@ -6873,32 +6863,32 @@
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="1:13">
-      <c r="B104" s="6">
+      <c r="B104" s="5">
         <v>322</v>
       </c>
       <c r="C104" t="s">
         <v>374</v>
       </c>
-      <c r="D104" s="6">
+      <c r="D104" s="5">
         <v>0.2</v>
       </c>
-      <c r="E104" s="6" t="s">
+      <c r="E104" s="5" t="s">
         <v>459</v>
       </c>
       <c r="F104" t="s">
         <v>460</v>
       </c>
-      <c r="G104" s="6">
+      <c r="G104" s="5">
         <v>220</v>
       </c>
-      <c r="H104" s="6">
+      <c r="H104" s="5">
         <v>109</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="J104" s="10"/>
-      <c r="K104" s="6">
+      <c r="J104" s="7"/>
+      <c r="K104" s="5">
         <v>0</v>
       </c>
       <c r="L104" t="s">
@@ -6909,596 +6899,596 @@
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="1:13">
-      <c r="B105" s="6">
+      <c r="B105" s="5">
         <v>323</v>
       </c>
       <c r="C105" t="s">
         <v>374</v>
       </c>
-      <c r="D105" s="6">
+      <c r="D105" s="5">
         <v>0.2</v>
       </c>
       <c r="E105" t="s">
         <v>463</v>
       </c>
-      <c r="F105" s="6" t="s">
+      <c r="F105" s="5" t="s">
         <v>464</v>
       </c>
-      <c r="G105" s="6">
+      <c r="G105" s="5">
         <v>285</v>
       </c>
-      <c r="H105" s="6">
+      <c r="H105" s="5">
         <v>142</v>
       </c>
-      <c r="I105" s="6">
+      <c r="I105" s="5">
         <v>40025</v>
       </c>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6">
+      <c r="J105" s="5"/>
+      <c r="K105" s="5">
         <v>0</v>
       </c>
       <c r="L105" t="s">
         <v>34</v>
       </c>
-      <c r="M105" s="6" t="s">
+      <c r="M105" s="5" t="s">
         <v>465</v>
       </c>
     </row>
-    <row r="106" s="4" customFormat="1" spans="1:13">
-      <c r="B106" s="6">
+    <row r="106" s="3" customFormat="1" spans="1:13">
+      <c r="B106" s="5">
         <v>324</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="C106" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D106" s="12">
+      <c r="D106" s="9">
         <v>0.2</v>
       </c>
-      <c r="E106" s="11" t="s">
+      <c r="E106" s="8" t="s">
         <v>466</v>
       </c>
-      <c r="F106" s="12" t="s">
+      <c r="F106" s="9" t="s">
         <v>467</v>
       </c>
-      <c r="G106" s="12">
+      <c r="G106" s="9">
         <v>260</v>
       </c>
-      <c r="H106" s="12">
+      <c r="H106" s="9">
         <v>130</v>
       </c>
-      <c r="I106" s="12" t="s">
+      <c r="I106" s="9" t="s">
         <v>468</v>
       </c>
-      <c r="J106" s="12"/>
-      <c r="K106" s="12">
-        <v>0</v>
-      </c>
-      <c r="L106" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M106" s="11" t="s">
+      <c r="J106" s="9"/>
+      <c r="K106" s="9">
+        <v>0</v>
+      </c>
+      <c r="L106" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M106" s="8" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="107" s="4" customFormat="1" spans="1:13">
-      <c r="B107" s="6">
+    <row r="107" s="3" customFormat="1" spans="1:13">
+      <c r="B107" s="5">
         <v>325</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D107" s="12">
+      <c r="D107" s="9">
         <v>0.2</v>
       </c>
-      <c r="E107" s="11" t="s">
+      <c r="E107" s="8" t="s">
         <v>470</v>
       </c>
-      <c r="F107" s="12" t="s">
+      <c r="F107" s="9" t="s">
         <v>471</v>
       </c>
-      <c r="G107" s="12">
+      <c r="G107" s="9">
         <v>260</v>
       </c>
-      <c r="H107" s="12">
+      <c r="H107" s="9">
         <v>130</v>
       </c>
-      <c r="I107" s="12" t="s">
+      <c r="I107" s="9" t="s">
         <v>472</v>
       </c>
-      <c r="J107" s="12"/>
-      <c r="K107" s="12">
-        <v>0</v>
-      </c>
-      <c r="L107" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M107" s="11" t="s">
+      <c r="J107" s="9"/>
+      <c r="K107" s="9">
+        <v>0</v>
+      </c>
+      <c r="L107" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M107" s="8" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="108" s="4" customFormat="1" spans="1:13">
-      <c r="B108" s="6">
+    <row r="108" s="3" customFormat="1" spans="1:13">
+      <c r="B108" s="5">
         <v>326</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C108" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D108" s="12">
+      <c r="D108" s="9">
         <v>0.2</v>
       </c>
-      <c r="E108" s="11" t="s">
+      <c r="E108" s="8" t="s">
         <v>474</v>
       </c>
-      <c r="F108" s="12" t="s">
+      <c r="F108" s="9" t="s">
         <v>475</v>
       </c>
-      <c r="G108" s="12">
+      <c r="G108" s="9">
         <v>260</v>
       </c>
-      <c r="H108" s="12">
+      <c r="H108" s="9">
         <v>130</v>
       </c>
-      <c r="I108" s="12" t="s">
+      <c r="I108" s="9" t="s">
         <v>476</v>
       </c>
-      <c r="J108" s="12">
+      <c r="J108" s="9">
         <v>106</v>
       </c>
-      <c r="K108" s="12">
-        <v>0</v>
-      </c>
-      <c r="L108" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M108" s="11" t="s">
+      <c r="K108" s="9">
+        <v>0</v>
+      </c>
+      <c r="L108" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M108" s="8" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="109" s="4" customFormat="1" spans="1:13">
-      <c r="B109" s="6">
+    <row r="109" s="3" customFormat="1" spans="1:13">
+      <c r="B109" s="5">
         <v>327</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C109" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D109" s="12">
+      <c r="D109" s="9">
         <v>0.2</v>
       </c>
-      <c r="E109" s="11" t="s">
+      <c r="E109" s="8" t="s">
         <v>478</v>
       </c>
-      <c r="F109" s="12" t="s">
+      <c r="F109" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="G109" s="12">
+      <c r="G109" s="9">
         <v>255</v>
       </c>
-      <c r="H109" s="12">
+      <c r="H109" s="9">
         <v>127</v>
       </c>
-      <c r="I109" s="12" t="s">
+      <c r="I109" s="9" t="s">
         <v>480</v>
       </c>
-      <c r="J109" s="12">
+      <c r="J109" s="9">
         <v>105</v>
       </c>
-      <c r="K109" s="12">
-        <v>0</v>
-      </c>
-      <c r="L109" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M109" s="11" t="s">
+      <c r="K109" s="9">
+        <v>0</v>
+      </c>
+      <c r="L109" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M109" s="8" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="110" s="4" customFormat="1" spans="1:13">
-      <c r="B110" s="6">
+    <row r="110" s="3" customFormat="1" spans="1:13">
+      <c r="B110" s="5">
         <v>328</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C110" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D110" s="12">
+      <c r="D110" s="9">
         <v>0.2</v>
       </c>
-      <c r="E110" s="11" t="s">
+      <c r="E110" s="8" t="s">
         <v>482</v>
       </c>
-      <c r="F110" s="12" t="s">
+      <c r="F110" s="9" t="s">
         <v>483</v>
       </c>
-      <c r="G110" s="12">
+      <c r="G110" s="9">
         <v>255</v>
       </c>
-      <c r="H110" s="12">
+      <c r="H110" s="9">
         <v>127</v>
       </c>
-      <c r="I110" s="12" t="s">
+      <c r="I110" s="9" t="s">
         <v>484</v>
       </c>
-      <c r="J110" s="12">
+      <c r="J110" s="9">
         <v>105</v>
       </c>
-      <c r="K110" s="12">
-        <v>0</v>
-      </c>
-      <c r="L110" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M110" s="11" t="s">
+      <c r="K110" s="9">
+        <v>0</v>
+      </c>
+      <c r="L110" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M110" s="8" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="111" s="4" customFormat="1" ht="14" customHeight="1" spans="1:13">
-      <c r="B111" s="6">
+    <row r="111" s="3" customFormat="1" ht="14" customHeight="1" spans="1:13">
+      <c r="B111" s="5">
         <v>329</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D111" s="12">
+      <c r="D111" s="9">
         <v>0.2</v>
       </c>
-      <c r="E111" s="11" t="s">
+      <c r="E111" s="8" t="s">
         <v>486</v>
       </c>
-      <c r="F111" s="12" t="s">
+      <c r="F111" s="9" t="s">
         <v>487</v>
       </c>
-      <c r="G111" s="12">
+      <c r="G111" s="9">
         <v>245</v>
       </c>
-      <c r="H111" s="12">
+      <c r="H111" s="9">
         <v>122</v>
       </c>
-      <c r="I111" s="12" t="s">
+      <c r="I111" s="9" t="s">
         <v>488</v>
       </c>
-      <c r="J111" s="12"/>
-      <c r="K111" s="12">
-        <v>0</v>
-      </c>
-      <c r="L111" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M111" s="11" t="s">
+      <c r="J111" s="9"/>
+      <c r="K111" s="9">
+        <v>0</v>
+      </c>
+      <c r="L111" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M111" s="8" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="112" s="4" customFormat="1" spans="1:13">
-      <c r="A112" s="11"/>
-      <c r="B112" s="6">
+    <row r="112" s="3" customFormat="1" spans="1:13">
+      <c r="A112" s="8"/>
+      <c r="B112" s="5">
         <v>330</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D112" s="12">
+      <c r="D112" s="9">
         <v>0.2</v>
       </c>
-      <c r="E112" s="11" t="s">
+      <c r="E112" s="8" t="s">
         <v>490</v>
       </c>
-      <c r="F112" s="11" t="s">
+      <c r="F112" s="8" t="s">
         <v>491</v>
       </c>
-      <c r="G112" s="12">
+      <c r="G112" s="9">
         <v>220</v>
       </c>
-      <c r="H112" s="12">
+      <c r="H112" s="9">
         <v>110</v>
       </c>
-      <c r="I112" s="12">
+      <c r="I112" s="9">
         <v>30041</v>
       </c>
-      <c r="K112" s="12">
-        <v>0</v>
-      </c>
-      <c r="L112" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M112" s="11" t="s">
+      <c r="K112" s="9">
+        <v>0</v>
+      </c>
+      <c r="L112" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M112" s="8" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="113" s="4" customFormat="1" spans="1:13">
-      <c r="A113" s="11"/>
-      <c r="B113" s="6">
+    <row r="113" s="3" customFormat="1" spans="1:13">
+      <c r="A113" s="8"/>
+      <c r="B113" s="5">
         <v>331</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C113" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D113" s="12">
+      <c r="D113" s="9">
         <v>0.2</v>
       </c>
-      <c r="E113" s="11" t="s">
+      <c r="E113" s="8" t="s">
         <v>493</v>
       </c>
-      <c r="F113" s="11" t="s">
+      <c r="F113" s="8" t="s">
         <v>494</v>
       </c>
-      <c r="G113" s="12">
+      <c r="G113" s="9">
         <v>200</v>
       </c>
-      <c r="H113" s="12">
+      <c r="H113" s="9">
         <v>100</v>
       </c>
-      <c r="I113" s="12" t="s">
+      <c r="I113" s="9" t="s">
         <v>495</v>
       </c>
-      <c r="K113" s="12">
-        <v>0</v>
-      </c>
-      <c r="L113" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M113" s="11" t="s">
+      <c r="K113" s="9">
+        <v>0</v>
+      </c>
+      <c r="L113" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M113" s="8" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="114" s="4" customFormat="1" spans="1:13">
-      <c r="A114" s="11"/>
-      <c r="B114" s="6">
+    <row r="114" s="3" customFormat="1" spans="1:13">
+      <c r="A114" s="8"/>
+      <c r="B114" s="5">
         <v>332</v>
       </c>
-      <c r="C114" s="11" t="s">
+      <c r="C114" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D114" s="12">
+      <c r="D114" s="9">
         <v>0.2</v>
       </c>
-      <c r="E114" s="11" t="s">
+      <c r="E114" s="8" t="s">
         <v>497</v>
       </c>
-      <c r="F114" s="11" t="s">
+      <c r="F114" s="8" t="s">
         <v>498</v>
       </c>
-      <c r="G114" s="12">
+      <c r="G114" s="9">
         <v>250</v>
       </c>
-      <c r="H114" s="12">
+      <c r="H114" s="9">
         <v>125</v>
       </c>
-      <c r="I114" s="12" t="s">
+      <c r="I114" s="9" t="s">
         <v>499</v>
       </c>
-      <c r="K114" s="12">
-        <v>0</v>
-      </c>
-      <c r="L114" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M114" s="11" t="s">
+      <c r="K114" s="9">
+        <v>0</v>
+      </c>
+      <c r="L114" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M114" s="8" t="s">
         <v>500</v>
       </c>
     </row>
-    <row r="115" s="4" customFormat="1" spans="1:13">
-      <c r="A115" s="11"/>
-      <c r="B115" s="6">
+    <row r="115" s="3" customFormat="1" spans="1:13">
+      <c r="A115" s="8"/>
+      <c r="B115" s="5">
         <v>333</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D115" s="12">
+      <c r="D115" s="9">
         <v>0.2</v>
       </c>
-      <c r="E115" s="11" t="s">
+      <c r="E115" s="8" t="s">
         <v>501</v>
       </c>
-      <c r="F115" s="11" t="s">
+      <c r="F115" s="8" t="s">
         <v>502</v>
       </c>
-      <c r="G115" s="12">
+      <c r="G115" s="9">
         <v>230</v>
       </c>
-      <c r="H115" s="12">
+      <c r="H115" s="9">
         <v>115</v>
       </c>
-      <c r="I115" s="12">
+      <c r="I115" s="9">
         <v>30046</v>
       </c>
-      <c r="K115" s="12">
-        <v>0</v>
-      </c>
-      <c r="L115" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M115" s="11" t="s">
+      <c r="K115" s="9">
+        <v>0</v>
+      </c>
+      <c r="L115" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M115" s="8" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="116" s="4" customFormat="1" spans="1:13">
-      <c r="A116" s="11"/>
-      <c r="B116" s="6">
+    <row r="116" s="3" customFormat="1" spans="1:13">
+      <c r="A116" s="8"/>
+      <c r="B116" s="5">
         <v>334</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C116" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D116" s="12">
+      <c r="D116" s="9">
         <v>0.2</v>
       </c>
-      <c r="E116" s="11" t="s">
+      <c r="E116" s="8" t="s">
         <v>504</v>
       </c>
-      <c r="F116" s="11" t="s">
+      <c r="F116" s="8" t="s">
         <v>505</v>
       </c>
-      <c r="G116" s="12">
+      <c r="G116" s="9">
         <v>210</v>
       </c>
-      <c r="H116" s="12">
+      <c r="H116" s="9">
         <v>105</v>
       </c>
-      <c r="I116" s="12">
+      <c r="I116" s="9">
         <v>30047</v>
       </c>
-      <c r="K116" s="12">
-        <v>0</v>
-      </c>
-      <c r="L116" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M116" s="11" t="s">
+      <c r="K116" s="9">
+        <v>0</v>
+      </c>
+      <c r="L116" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M116" s="8" t="s">
         <v>506</v>
       </c>
     </row>
-    <row r="117" s="4" customFormat="1" spans="1:13">
-      <c r="A117" s="11"/>
-      <c r="B117" s="6">
+    <row r="117" s="3" customFormat="1" spans="1:13">
+      <c r="A117" s="8"/>
+      <c r="B117" s="5">
         <v>335</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D117" s="12">
+      <c r="D117" s="9">
         <v>0.2</v>
       </c>
-      <c r="E117" s="11" t="s">
+      <c r="E117" s="8" t="s">
         <v>507</v>
       </c>
-      <c r="F117" s="11" t="s">
+      <c r="F117" s="8" t="s">
         <v>508</v>
       </c>
-      <c r="G117" s="12">
+      <c r="G117" s="9">
         <v>220</v>
       </c>
-      <c r="H117" s="12">
+      <c r="H117" s="9">
         <v>110</v>
       </c>
-      <c r="I117" s="12">
+      <c r="I117" s="9">
         <v>30048</v>
       </c>
-      <c r="K117" s="12">
-        <v>0</v>
-      </c>
-      <c r="L117" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M117" s="11" t="s">
+      <c r="K117" s="9">
+        <v>0</v>
+      </c>
+      <c r="L117" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M117" s="8" t="s">
         <v>509</v>
       </c>
     </row>
-    <row r="118" s="4" customFormat="1" spans="1:13">
-      <c r="A118" s="11"/>
-      <c r="B118" s="6">
+    <row r="118" s="3" customFormat="1" spans="1:13">
+      <c r="A118" s="8"/>
+      <c r="B118" s="5">
         <v>336</v>
       </c>
-      <c r="C118" s="11" t="s">
+      <c r="C118" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D118" s="12">
+      <c r="D118" s="9">
         <v>0.2</v>
       </c>
-      <c r="E118" s="11" t="s">
+      <c r="E118" s="8" t="s">
         <v>510</v>
       </c>
-      <c r="F118" s="11" t="s">
+      <c r="F118" s="8" t="s">
         <v>511</v>
       </c>
-      <c r="G118" s="12">
+      <c r="G118" s="9">
         <v>230</v>
       </c>
-      <c r="H118" s="12">
+      <c r="H118" s="9">
         <v>115</v>
       </c>
-      <c r="I118" s="12">
+      <c r="I118" s="9">
         <v>30049</v>
       </c>
-      <c r="K118" s="12">
-        <v>0</v>
-      </c>
-      <c r="L118" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M118" s="11" t="s">
+      <c r="K118" s="9">
+        <v>0</v>
+      </c>
+      <c r="L118" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M118" s="8" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="119" s="4" customFormat="1" spans="1:13">
-      <c r="A119" s="11"/>
-      <c r="B119" s="6">
+    <row r="119" s="3" customFormat="1" spans="1:13">
+      <c r="A119" s="8"/>
+      <c r="B119" s="5">
         <v>337</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C119" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D119" s="12">
+      <c r="D119" s="9">
         <v>0.2</v>
       </c>
-      <c r="E119" s="11" t="s">
+      <c r="E119" s="8" t="s">
         <v>513</v>
       </c>
-      <c r="F119" s="11" t="s">
+      <c r="F119" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="G119" s="12">
+      <c r="G119" s="9">
         <v>220</v>
       </c>
-      <c r="H119" s="12">
+      <c r="H119" s="9">
         <v>110</v>
       </c>
-      <c r="I119" s="12">
+      <c r="I119" s="9">
         <v>30053</v>
       </c>
-      <c r="K119" s="12">
-        <v>0</v>
-      </c>
-      <c r="L119" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M119" s="11" t="s">
+      <c r="K119" s="9">
+        <v>0</v>
+      </c>
+      <c r="L119" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M119" s="8" t="s">
         <v>515</v>
       </c>
     </row>
-    <row r="120" s="4" customFormat="1" spans="1:13">
-      <c r="A120" s="11"/>
-      <c r="B120" s="6">
+    <row r="120" s="3" customFormat="1" spans="1:13">
+      <c r="A120" s="8"/>
+      <c r="B120" s="5">
         <v>338</v>
       </c>
-      <c r="C120" s="11" t="s">
+      <c r="C120" s="8" t="s">
         <v>374</v>
       </c>
-      <c r="D120" s="12">
+      <c r="D120" s="9">
         <v>0.2</v>
       </c>
-      <c r="E120" s="11" t="s">
+      <c r="E120" s="8" t="s">
         <v>516</v>
       </c>
-      <c r="F120" s="11" t="s">
+      <c r="F120" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="G120" s="12">
+      <c r="G120" s="9">
         <v>200</v>
       </c>
-      <c r="H120" s="12">
+      <c r="H120" s="9">
         <v>100</v>
       </c>
-      <c r="I120" s="12">
+      <c r="I120" s="9">
         <v>30054</v>
       </c>
-      <c r="K120" s="12">
-        <v>0</v>
-      </c>
-      <c r="L120" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M120" s="11" t="s">
+      <c r="K120" s="9">
+        <v>0</v>
+      </c>
+      <c r="L120" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M120" s="8" t="s">
         <v>518</v>
       </c>
     </row>
     <row r="121" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:13">
-      <c r="D121" s="6"/>
-      <c r="E121" s="6"/>
-      <c r="F121" s="6"/>
-      <c r="G121" s="6"/>
-      <c r="H121" s="6"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="M121" s="6"/>
+      <c r="D121" s="5"/>
+      <c r="E121" s="5"/>
+      <c r="F121" s="5"/>
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
+      <c r="J121" s="5"/>
+      <c r="K121" s="5"/>
+      <c r="M121" s="5"/>
     </row>
     <row r="122" s="1" customFormat="1" spans="1:13">
       <c r="B122" s="1" t="s">
@@ -7507,28 +7497,28 @@
       <c r="C122" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D122" s="6">
+      <c r="D122" s="5">
         <v>0.1</v>
       </c>
-      <c r="E122" s="6">
+      <c r="E122" s="5">
         <v>235</v>
       </c>
-      <c r="F122" s="6" t="s">
+      <c r="F122" s="5" t="s">
         <v>521</v>
       </c>
-      <c r="G122" s="6">
+      <c r="G122" s="5">
         <v>660</v>
       </c>
-      <c r="H122" s="6">
+      <c r="H122" s="5">
         <v>330</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>522</v>
       </c>
-      <c r="J122" s="6">
+      <c r="J122" s="5">
         <v>101</v>
       </c>
-      <c r="K122" s="6">
+      <c r="K122" s="5">
         <v>0</v>
       </c>
       <c r="L122" t="s">
@@ -7545,26 +7535,26 @@
       <c r="C123" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D123" s="5">
         <v>0.1</v>
       </c>
-      <c r="E123" s="6" t="s">
+      <c r="E123" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="F123" s="6" t="s">
+      <c r="F123" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="G123" s="6">
+      <c r="G123" s="5">
         <v>585</v>
       </c>
-      <c r="H123" s="6">
+      <c r="H123" s="5">
         <v>292</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="J123" s="6"/>
-      <c r="K123" s="6">
+      <c r="J123" s="5"/>
+      <c r="K123" s="5">
         <v>0</v>
       </c>
       <c r="L123" t="s">
@@ -7581,31 +7571,31 @@
       <c r="C124" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D124" s="6">
+      <c r="D124" s="5">
         <v>0.1</v>
       </c>
-      <c r="E124" s="6" t="s">
+      <c r="E124" s="5" t="s">
         <v>530</v>
       </c>
-      <c r="F124" s="6" t="s">
+      <c r="F124" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="G124" s="6">
+      <c r="G124" s="5">
         <v>625</v>
       </c>
-      <c r="H124" s="6">
+      <c r="H124" s="5">
         <v>312</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>532</v>
       </c>
-      <c r="K124" s="6">
+      <c r="K124" s="5">
         <v>0</v>
       </c>
       <c r="L124" t="s">
         <v>34</v>
       </c>
-      <c r="M124" s="6" t="s">
+      <c r="M124" s="5" t="s">
         <v>533</v>
       </c>
     </row>
@@ -7616,26 +7606,26 @@
       <c r="C125" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D125" s="5">
         <v>0.1</v>
       </c>
-      <c r="E125" s="6" t="s">
+      <c r="E125" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="F125" s="6" t="s">
+      <c r="F125" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="G125" s="6">
+      <c r="G125" s="5">
         <v>520</v>
       </c>
-      <c r="H125" s="6">
+      <c r="H125" s="5">
         <v>260</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>537</v>
       </c>
-      <c r="J125" s="6"/>
-      <c r="K125" s="6">
+      <c r="J125" s="5"/>
+      <c r="K125" s="5">
         <v>0</v>
       </c>
       <c r="L125" t="s">
@@ -7652,26 +7642,26 @@
       <c r="C126" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D126" s="6">
+      <c r="D126" s="5">
         <v>0.1</v>
       </c>
-      <c r="E126" s="6" t="s">
+      <c r="E126" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="F126" s="6" t="s">
+      <c r="F126" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="G126" s="6">
+      <c r="G126" s="5">
         <v>465</v>
       </c>
-      <c r="H126" s="6">
+      <c r="H126" s="5">
         <v>232</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>542</v>
       </c>
-      <c r="J126" s="6"/>
-      <c r="K126" s="6">
+      <c r="J126" s="5"/>
+      <c r="K126" s="5">
         <v>0</v>
       </c>
       <c r="L126" t="s">
@@ -7688,34 +7678,34 @@
       <c r="C127" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D127" s="6">
+      <c r="D127" s="5">
         <v>0.1</v>
       </c>
-      <c r="E127" s="6" t="s">
+      <c r="E127" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="F127" s="6" t="s">
+      <c r="F127" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="G127" s="6">
+      <c r="G127" s="5">
         <v>625</v>
       </c>
-      <c r="H127" s="6">
+      <c r="H127" s="5">
         <v>312</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>547</v>
       </c>
-      <c r="J127" s="6">
+      <c r="J127" s="5">
         <v>105</v>
       </c>
-      <c r="K127" s="6">
+      <c r="K127" s="5">
         <v>0</v>
       </c>
       <c r="L127" t="s">
         <v>34</v>
       </c>
-      <c r="M127" s="6" t="s">
+      <c r="M127" s="5" t="s">
         <v>548</v>
       </c>
     </row>
@@ -7726,25 +7716,25 @@
       <c r="C128" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D128" s="6">
+      <c r="D128" s="5">
         <v>0.1</v>
       </c>
-      <c r="E128" s="6" t="s">
+      <c r="E128" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="F128" s="6" t="s">
+      <c r="F128" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="G128" s="6">
+      <c r="G128" s="5">
         <v>395</v>
       </c>
-      <c r="H128" s="6">
+      <c r="H128" s="5">
         <v>197</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>552</v>
       </c>
-      <c r="K128" s="6">
+      <c r="K128" s="5">
         <v>0</v>
       </c>
       <c r="L128" t="s">
@@ -7761,25 +7751,25 @@
       <c r="C129" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D129" s="6">
+      <c r="D129" s="5">
         <v>0.1</v>
       </c>
-      <c r="E129" s="6" t="s">
+      <c r="E129" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="F129" s="6" t="s">
+      <c r="F129" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="G129" s="6">
+      <c r="G129" s="5">
         <v>405</v>
       </c>
-      <c r="H129" s="6">
+      <c r="H129" s="5">
         <v>202</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>557</v>
       </c>
-      <c r="K129" s="6">
+      <c r="K129" s="5">
         <v>0</v>
       </c>
       <c r="L129" t="s">
@@ -7796,26 +7786,26 @@
       <c r="C130" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D130" s="6">
+      <c r="D130" s="5">
         <v>0.1</v>
       </c>
-      <c r="E130" s="6" t="s">
+      <c r="E130" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="F130" s="6" t="s">
+      <c r="F130" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="G130" s="6">
+      <c r="G130" s="5">
         <v>480</v>
       </c>
-      <c r="H130" s="6">
+      <c r="H130" s="5">
         <v>240</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="J130" s="6"/>
-      <c r="K130" s="6">
+      <c r="J130" s="5"/>
+      <c r="K130" s="5">
         <v>0</v>
       </c>
       <c r="L130" t="s">
@@ -7832,26 +7822,26 @@
       <c r="C131" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D131" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E131" s="6" t="s">
+      <c r="D131" s="5">
+        <v>0</v>
+      </c>
+      <c r="E131" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="F131" s="6" t="s">
+      <c r="F131" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="G131" s="6">
+      <c r="G131" s="5">
         <v>520</v>
       </c>
-      <c r="H131" s="6">
+      <c r="H131" s="5">
         <v>260</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>567</v>
       </c>
-      <c r="J131" s="6"/>
-      <c r="K131" s="6">
+      <c r="J131" s="5"/>
+      <c r="K131" s="5">
         <v>0</v>
       </c>
       <c r="L131" t="s">
@@ -7868,25 +7858,25 @@
       <c r="C132" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D132" s="6">
+      <c r="D132" s="5">
         <v>0.1</v>
       </c>
-      <c r="E132" s="6" t="s">
+      <c r="E132" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="F132" s="6" t="s">
+      <c r="F132" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="G132" s="6">
+      <c r="G132" s="5">
         <v>350</v>
       </c>
-      <c r="H132" s="6">
+      <c r="H132" s="5">
         <v>175</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="K132" s="6">
+      <c r="K132" s="5">
         <v>0</v>
       </c>
       <c r="L132" t="s">
@@ -7903,25 +7893,25 @@
       <c r="C133" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D133" s="6">
+      <c r="D133" s="5">
         <v>0.1</v>
       </c>
-      <c r="E133" s="6" t="s">
+      <c r="E133" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="F133" s="6" t="s">
+      <c r="F133" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="G133" s="6">
+      <c r="G133" s="5">
         <v>395</v>
       </c>
-      <c r="H133" s="6">
+      <c r="H133" s="5">
         <v>197</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>577</v>
       </c>
-      <c r="K133" s="6">
+      <c r="K133" s="5">
         <v>0</v>
       </c>
       <c r="L133" t="s">
@@ -7938,25 +7928,25 @@
       <c r="C134" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D134" s="6">
+      <c r="D134" s="5">
         <v>0.1</v>
       </c>
       <c r="E134" t="s">
         <v>580</v>
       </c>
-      <c r="F134" s="6" t="s">
+      <c r="F134" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="G134" s="6">
+      <c r="G134" s="5">
         <v>625</v>
       </c>
-      <c r="H134" s="6">
+      <c r="H134" s="5">
         <v>312</v>
       </c>
-      <c r="I134" s="6" t="s">
+      <c r="I134" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="K134" s="6">
+      <c r="K134" s="5">
         <v>0</v>
       </c>
       <c r="L134" t="s">
@@ -7973,31 +7963,31 @@
       <c r="C135" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D135" s="6">
+      <c r="D135" s="5">
         <v>0.1</v>
       </c>
       <c r="E135" t="s">
         <v>585</v>
       </c>
-      <c r="F135" s="6" t="s">
+      <c r="F135" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="G135" s="6">
+      <c r="G135" s="5">
         <v>395</v>
       </c>
-      <c r="H135" s="6">
+      <c r="H135" s="5">
         <v>197</v>
       </c>
-      <c r="I135" s="6">
+      <c r="I135" s="5">
         <v>40016</v>
       </c>
-      <c r="K135" s="6">
+      <c r="K135" s="5">
         <v>0</v>
       </c>
       <c r="L135" t="s">
         <v>34</v>
       </c>
-      <c r="M135" s="6" t="s">
+      <c r="M135" s="5" t="s">
         <v>587</v>
       </c>
     </row>
@@ -8008,25 +7998,25 @@
       <c r="C136" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D136" s="6">
+      <c r="D136" s="5">
         <v>0.1</v>
       </c>
       <c r="E136" t="s">
         <v>589</v>
       </c>
-      <c r="F136" s="6" t="s">
+      <c r="F136" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="G136" s="6">
+      <c r="G136" s="5">
         <v>405</v>
       </c>
-      <c r="H136" s="6">
+      <c r="H136" s="5">
         <v>202</v>
       </c>
-      <c r="I136" s="6">
+      <c r="I136" s="5">
         <v>40017</v>
       </c>
-      <c r="K136" s="6">
+      <c r="K136" s="5">
         <v>0</v>
       </c>
       <c r="L136" t="s">
@@ -8043,34 +8033,34 @@
       <c r="C137" s="1" t="s">
         <v>520</v>
       </c>
-      <c r="D137" s="6">
+      <c r="D137" s="5">
         <v>0.1</v>
       </c>
       <c r="E137" t="s">
         <v>593</v>
       </c>
-      <c r="F137" s="6" t="s">
+      <c r="F137" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="G137" s="6">
+      <c r="G137" s="5">
         <v>585</v>
       </c>
-      <c r="H137" s="6">
+      <c r="H137" s="5">
         <v>292</v>
       </c>
-      <c r="I137" s="6">
+      <c r="I137" s="5">
         <v>40024</v>
       </c>
-      <c r="J137" s="6">
+      <c r="J137" s="5">
         <v>107</v>
       </c>
-      <c r="K137" s="6">
+      <c r="K137" s="5">
         <v>0</v>
       </c>
       <c r="L137" t="s">
         <v>34</v>
       </c>
-      <c r="M137" s="6" t="s">
+      <c r="M137" s="5" t="s">
         <v>595</v>
       </c>
     </row>
@@ -8081,7 +8071,7 @@
       <c r="C138" t="s">
         <v>520</v>
       </c>
-      <c r="D138" s="6">
+      <c r="D138" s="5">
         <v>0.1</v>
       </c>
       <c r="E138" t="s">
@@ -8090,16 +8080,16 @@
       <c r="F138" t="s">
         <v>598</v>
       </c>
-      <c r="G138" s="6">
+      <c r="G138" s="5">
         <v>480</v>
       </c>
-      <c r="H138" s="6">
+      <c r="H138" s="5">
         <v>240</v>
       </c>
-      <c r="I138" s="6">
+      <c r="I138" s="5">
         <v>40026</v>
       </c>
-      <c r="K138" s="6">
+      <c r="K138" s="5">
         <v>1</v>
       </c>
       <c r="L138" t="s">
@@ -8116,7 +8106,7 @@
       <c r="C139" t="s">
         <v>520</v>
       </c>
-      <c r="D139" s="6">
+      <c r="D139" s="5">
         <v>0.1</v>
       </c>
       <c r="E139" t="s">
@@ -8125,16 +8115,16 @@
       <c r="F139" t="s">
         <v>602</v>
       </c>
-      <c r="G139" s="6">
+      <c r="G139" s="5">
         <v>430</v>
       </c>
-      <c r="H139" s="6">
+      <c r="H139" s="5">
         <v>215</v>
       </c>
-      <c r="I139" s="6">
+      <c r="I139" s="5">
         <v>40027</v>
       </c>
-      <c r="K139" s="6">
+      <c r="K139" s="5">
         <v>1</v>
       </c>
       <c r="L139" t="s">
@@ -8151,7 +8141,7 @@
       <c r="C140" t="s">
         <v>520</v>
       </c>
-      <c r="D140" s="6">
+      <c r="D140" s="5">
         <v>0.1</v>
       </c>
       <c r="E140" t="s">
@@ -8160,16 +8150,16 @@
       <c r="F140" t="s">
         <v>606</v>
       </c>
-      <c r="G140" s="6">
+      <c r="G140" s="5">
         <v>380</v>
       </c>
-      <c r="H140" s="6">
+      <c r="H140" s="5">
         <v>190</v>
       </c>
-      <c r="I140" s="6">
+      <c r="I140" s="5">
         <v>40028</v>
       </c>
-      <c r="K140" s="6">
+      <c r="K140" s="5">
         <v>2</v>
       </c>
       <c r="L140" t="s">
@@ -8186,7 +8176,7 @@
       <c r="C141" t="s">
         <v>520</v>
       </c>
-      <c r="D141" s="6">
+      <c r="D141" s="5">
         <v>0.1</v>
       </c>
       <c r="E141" t="s">
@@ -8195,16 +8185,16 @@
       <c r="F141" t="s">
         <v>610</v>
       </c>
-      <c r="G141" s="6">
+      <c r="G141" s="5">
         <v>385</v>
       </c>
-      <c r="H141" s="6">
+      <c r="H141" s="5">
         <v>192</v>
       </c>
-      <c r="I141" s="6">
+      <c r="I141" s="5">
         <v>40029</v>
       </c>
-      <c r="K141" s="6">
+      <c r="K141" s="5">
         <v>2</v>
       </c>
       <c r="L141" t="s">
@@ -8221,7 +8211,7 @@
       <c r="C142" t="s">
         <v>520</v>
       </c>
-      <c r="D142" s="6">
+      <c r="D142" s="5">
         <v>0.1</v>
       </c>
       <c r="E142" t="s">
@@ -8230,16 +8220,16 @@
       <c r="F142" t="s">
         <v>614</v>
       </c>
-      <c r="G142" s="6">
+      <c r="G142" s="5">
         <v>395</v>
       </c>
-      <c r="H142" s="6">
+      <c r="H142" s="5">
         <v>197</v>
       </c>
-      <c r="I142" s="6">
+      <c r="I142" s="5">
         <v>40030</v>
       </c>
-      <c r="K142" s="6">
+      <c r="K142" s="5">
         <v>0</v>
       </c>
       <c r="L142" t="s">
@@ -8257,13 +8247,13 @@
       <c r="C143" t="s">
         <v>520</v>
       </c>
-      <c r="D143" s="6">
+      <c r="D143" s="5">
         <v>0.1</v>
       </c>
-      <c r="E143" s="6" t="s">
+      <c r="E143" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="F143" s="6" t="s">
+      <c r="F143" s="5" t="s">
         <v>618</v>
       </c>
       <c r="G143" s="1">
@@ -8272,10 +8262,10 @@
       <c r="H143" s="1">
         <v>210</v>
       </c>
-      <c r="I143" s="6">
+      <c r="I143" s="5">
         <v>40031</v>
       </c>
-      <c r="K143" s="6">
+      <c r="K143" s="5">
         <v>0</v>
       </c>
       <c r="L143" t="s">
@@ -8292,7 +8282,7 @@
       <c r="C144" t="s">
         <v>520</v>
       </c>
-      <c r="D144" s="6">
+      <c r="D144" s="5">
         <v>0.1</v>
       </c>
       <c r="E144" t="s">
@@ -8301,10 +8291,10 @@
       <c r="F144" s="1" t="s">
         <v>622</v>
       </c>
-      <c r="G144" s="6">
+      <c r="G144" s="5">
         <v>550</v>
       </c>
-      <c r="H144" s="6">
+      <c r="H144" s="5">
         <v>275</v>
       </c>
       <c r="I144" s="1" t="s">
@@ -8327,7 +8317,7 @@
       <c r="C145" t="s">
         <v>520</v>
       </c>
-      <c r="D145" s="6">
+      <c r="D145" s="5">
         <v>0.1</v>
       </c>
       <c r="E145" t="s">
@@ -8336,10 +8326,10 @@
       <c r="F145" s="1" t="s">
         <v>628</v>
       </c>
-      <c r="G145" s="6">
+      <c r="G145" s="5">
         <v>550</v>
       </c>
-      <c r="H145" s="6">
+      <c r="H145" s="5">
         <v>275</v>
       </c>
       <c r="I145" s="1" t="s">
@@ -8362,25 +8352,25 @@
       <c r="C146" t="s">
         <v>520</v>
       </c>
-      <c r="D146" s="6">
+      <c r="D146" s="5">
         <v>0.1</v>
       </c>
-      <c r="E146" s="6" t="s">
+      <c r="E146" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="F146" s="6" t="s">
+      <c r="F146" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="G146" s="6">
+      <c r="G146" s="5">
         <v>550</v>
       </c>
-      <c r="H146" s="6">
+      <c r="H146" s="5">
         <v>275</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>634</v>
       </c>
-      <c r="K146" s="6">
+      <c r="K146" s="5">
         <v>0</v>
       </c>
       <c r="L146" t="s">
@@ -8390,441 +8380,441 @@
         <v>635</v>
       </c>
     </row>
-    <row r="147" s="4" customFormat="1" spans="1:13">
+    <row r="147" s="3" customFormat="1" spans="1:13">
       <c r="B147" s="1" t="s">
         <v>636</v>
       </c>
-      <c r="C147" s="11" t="s">
+      <c r="C147" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D147" s="12">
+      <c r="D147" s="9">
         <v>0.1</v>
       </c>
-      <c r="E147" s="11" t="s">
+      <c r="E147" s="8" t="s">
         <v>637</v>
       </c>
-      <c r="F147" s="12" t="s">
+      <c r="F147" s="9" t="s">
         <v>638</v>
       </c>
-      <c r="G147" s="12">
+      <c r="G147" s="9">
         <v>395</v>
       </c>
-      <c r="H147" s="12">
+      <c r="H147" s="9">
         <v>197</v>
       </c>
-      <c r="I147" s="12" t="s">
+      <c r="I147" s="9" t="s">
         <v>639</v>
       </c>
-      <c r="J147" s="12"/>
-      <c r="K147" s="4" t="s">
+      <c r="J147" s="9"/>
+      <c r="K147" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="L147" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M147" s="11" t="s">
+      <c r="L147" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M147" s="8" t="s">
         <v>640</v>
       </c>
     </row>
-    <row r="148" s="4" customFormat="1" spans="1:13">
+    <row r="148" s="3" customFormat="1" spans="1:13">
       <c r="B148" s="1" t="s">
         <v>641</v>
       </c>
-      <c r="C148" s="11" t="s">
+      <c r="C148" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D148" s="12">
+      <c r="D148" s="9">
         <v>0.1</v>
       </c>
-      <c r="E148" s="11" t="s">
+      <c r="E148" s="8" t="s">
         <v>642</v>
       </c>
-      <c r="F148" s="12" t="s">
+      <c r="F148" s="9" t="s">
         <v>643</v>
       </c>
-      <c r="G148" s="12">
+      <c r="G148" s="9">
         <v>480</v>
       </c>
-      <c r="H148" s="12">
+      <c r="H148" s="9">
         <v>240</v>
       </c>
-      <c r="I148" s="12" t="s">
+      <c r="I148" s="9" t="s">
         <v>644</v>
       </c>
-      <c r="J148" s="12"/>
-      <c r="K148" s="4" t="s">
+      <c r="J148" s="9"/>
+      <c r="K148" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="L148" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M148" s="11" t="s">
+      <c r="L148" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M148" s="8" t="s">
         <v>645</v>
       </c>
     </row>
-    <row r="149" s="4" customFormat="1" spans="1:13">
+    <row r="149" s="3" customFormat="1" spans="1:13">
       <c r="B149" s="1" t="s">
         <v>646</v>
       </c>
-      <c r="C149" s="11" t="s">
+      <c r="C149" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D149" s="12">
+      <c r="D149" s="9">
         <v>0.1</v>
       </c>
-      <c r="E149" s="11" t="s">
+      <c r="E149" s="8" t="s">
         <v>647</v>
       </c>
-      <c r="F149" s="12" t="s">
+      <c r="F149" s="9" t="s">
         <v>648</v>
       </c>
-      <c r="G149" s="12">
+      <c r="G149" s="9">
         <v>480</v>
       </c>
-      <c r="H149" s="12">
+      <c r="H149" s="9">
         <v>240</v>
       </c>
-      <c r="I149" s="12" t="s">
+      <c r="I149" s="9" t="s">
         <v>649</v>
       </c>
-      <c r="J149" s="12"/>
-      <c r="K149" s="4" t="s">
+      <c r="J149" s="9"/>
+      <c r="K149" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="L149" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M149" s="11" t="s">
+      <c r="L149" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M149" s="8" t="s">
         <v>650</v>
       </c>
     </row>
-    <row r="150" s="4" customFormat="1" spans="1:13">
+    <row r="150" s="3" customFormat="1" spans="1:13">
       <c r="B150" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="C150" s="11" t="s">
+      <c r="C150" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D150" s="12">
+      <c r="D150" s="9">
         <v>0.1</v>
       </c>
-      <c r="E150" s="11" t="s">
+      <c r="E150" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="F150" s="12" t="s">
+      <c r="F150" s="9" t="s">
         <v>653</v>
       </c>
-      <c r="G150" s="12">
+      <c r="G150" s="9">
         <v>480</v>
       </c>
-      <c r="H150" s="12">
+      <c r="H150" s="9">
         <v>240</v>
       </c>
-      <c r="I150" s="12" t="s">
+      <c r="I150" s="9" t="s">
         <v>654</v>
       </c>
-      <c r="J150" s="12"/>
-      <c r="K150" s="4" t="s">
+      <c r="J150" s="9"/>
+      <c r="K150" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="L150" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M150" s="11" t="s">
+      <c r="L150" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M150" s="8" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="151" s="4" customFormat="1" spans="1:13">
+    <row r="151" s="3" customFormat="1" spans="1:13">
       <c r="B151" s="1" t="s">
         <v>656</v>
       </c>
-      <c r="C151" s="11" t="s">
+      <c r="C151" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D151" s="12">
+      <c r="D151" s="9">
         <v>0.1</v>
       </c>
-      <c r="E151" s="11" t="s">
+      <c r="E151" s="8" t="s">
         <v>657</v>
       </c>
-      <c r="F151" s="12" t="s">
+      <c r="F151" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="G151" s="12">
+      <c r="G151" s="9">
         <v>480</v>
       </c>
-      <c r="H151" s="12">
+      <c r="H151" s="9">
         <v>240</v>
       </c>
-      <c r="I151" s="12" t="s">
+      <c r="I151" s="9" t="s">
         <v>659</v>
       </c>
-      <c r="J151" s="12"/>
-      <c r="K151" s="4" t="s">
+      <c r="J151" s="9"/>
+      <c r="K151" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="L151" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M151" s="11" t="s">
+      <c r="L151" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M151" s="8" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="152" s="4" customFormat="1" spans="1:13">
+    <row r="152" s="3" customFormat="1" spans="1:13">
       <c r="B152" s="1" t="s">
         <v>661</v>
       </c>
-      <c r="C152" s="11" t="s">
+      <c r="C152" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D152" s="12">
+      <c r="D152" s="9">
         <v>0.1</v>
       </c>
-      <c r="E152" s="11" t="s">
+      <c r="E152" s="8" t="s">
         <v>662</v>
       </c>
-      <c r="F152" s="12" t="s">
+      <c r="F152" s="9" t="s">
         <v>663</v>
       </c>
-      <c r="G152" s="12">
+      <c r="G152" s="9">
         <v>480</v>
       </c>
-      <c r="H152" s="12">
+      <c r="H152" s="9">
         <v>240</v>
       </c>
-      <c r="I152" s="12" t="s">
+      <c r="I152" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="J152" s="12"/>
-      <c r="K152" s="4" t="s">
+      <c r="J152" s="9"/>
+      <c r="K152" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="L152" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M152" s="11" t="s">
+      <c r="L152" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M152" s="8" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="153" s="4" customFormat="1" spans="1:13">
-      <c r="A153" s="11"/>
+    <row r="153" s="3" customFormat="1" spans="1:13">
+      <c r="A153" s="8"/>
       <c r="B153" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="C153" s="11" t="s">
+      <c r="C153" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D153" s="12">
+      <c r="D153" s="9">
         <v>0.1</v>
       </c>
-      <c r="E153" s="11" t="s">
+      <c r="E153" s="8" t="s">
         <v>667</v>
       </c>
-      <c r="F153" s="11" t="s">
+      <c r="F153" s="8" t="s">
         <v>668</v>
       </c>
-      <c r="G153" s="12">
+      <c r="G153" s="9">
         <v>450</v>
       </c>
-      <c r="H153" s="12">
+      <c r="H153" s="9">
         <v>225</v>
       </c>
-      <c r="I153" s="12">
+      <c r="I153" s="9">
         <v>40039</v>
       </c>
-      <c r="J153" s="12"/>
-      <c r="K153" s="12">
-        <v>0</v>
-      </c>
-      <c r="L153" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M153" s="11" t="s">
+      <c r="J153" s="9"/>
+      <c r="K153" s="9">
+        <v>0</v>
+      </c>
+      <c r="L153" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M153" s="8" t="s">
         <v>669</v>
       </c>
     </row>
-    <row r="154" s="4" customFormat="1" spans="1:13">
-      <c r="A154" s="11"/>
+    <row r="154" s="3" customFormat="1" spans="1:13">
+      <c r="A154" s="8"/>
       <c r="B154" s="1" t="s">
         <v>670</v>
       </c>
-      <c r="C154" s="11" t="s">
+      <c r="C154" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D154" s="12">
+      <c r="D154" s="9">
         <v>0.1</v>
       </c>
-      <c r="E154" s="11" t="s">
+      <c r="E154" s="8" t="s">
         <v>671</v>
       </c>
-      <c r="F154" s="11" t="s">
+      <c r="F154" s="8" t="s">
         <v>672</v>
       </c>
-      <c r="G154" s="12">
+      <c r="G154" s="9">
         <v>400</v>
       </c>
-      <c r="H154" s="12">
+      <c r="H154" s="9">
         <v>200</v>
       </c>
-      <c r="I154" s="12">
+      <c r="I154" s="9">
         <v>40040</v>
       </c>
-      <c r="J154" s="12"/>
-      <c r="K154" s="12">
-        <v>0</v>
-      </c>
-      <c r="L154" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M154" s="11" t="s">
+      <c r="J154" s="9"/>
+      <c r="K154" s="9">
+        <v>0</v>
+      </c>
+      <c r="L154" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M154" s="8" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="155" s="4" customFormat="1" spans="1:13">
-      <c r="A155" s="11"/>
+    <row r="155" s="3" customFormat="1" spans="1:13">
+      <c r="A155" s="8"/>
       <c r="B155" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="C155" s="11" t="s">
+      <c r="C155" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D155" s="12">
+      <c r="D155" s="9">
         <v>0.1</v>
       </c>
-      <c r="E155" s="11" t="s">
+      <c r="E155" s="8" t="s">
         <v>675</v>
       </c>
-      <c r="F155" s="11" t="s">
+      <c r="F155" s="8" t="s">
         <v>676</v>
       </c>
-      <c r="G155" s="12">
+      <c r="G155" s="9">
         <v>480</v>
       </c>
-      <c r="H155" s="12">
+      <c r="H155" s="9">
         <v>240</v>
       </c>
-      <c r="I155" s="12">
+      <c r="I155" s="9">
         <v>40041</v>
       </c>
-      <c r="J155" s="12"/>
-      <c r="K155" s="12">
-        <v>0</v>
-      </c>
-      <c r="L155" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M155" s="11" t="s">
+      <c r="J155" s="9"/>
+      <c r="K155" s="9">
+        <v>0</v>
+      </c>
+      <c r="L155" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M155" s="8" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="156" s="4" customFormat="1" spans="1:13">
-      <c r="A156" s="11"/>
+    <row r="156" s="3" customFormat="1" spans="1:13">
+      <c r="A156" s="8"/>
       <c r="B156" s="1" t="s">
         <v>678</v>
       </c>
-      <c r="C156" s="11" t="s">
+      <c r="C156" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D156" s="12">
+      <c r="D156" s="9">
         <v>0.1</v>
       </c>
-      <c r="E156" s="11" t="s">
+      <c r="E156" s="8" t="s">
         <v>679</v>
       </c>
-      <c r="F156" s="11" t="s">
+      <c r="F156" s="8" t="s">
         <v>680</v>
       </c>
-      <c r="G156" s="12">
+      <c r="G156" s="9">
         <v>430</v>
       </c>
-      <c r="H156" s="12">
+      <c r="H156" s="9">
         <v>215</v>
       </c>
-      <c r="I156" s="12">
+      <c r="I156" s="9">
         <v>40042</v>
       </c>
-      <c r="J156" s="12"/>
-      <c r="K156" s="12">
-        <v>0</v>
-      </c>
-      <c r="L156" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M156" s="11" t="s">
+      <c r="J156" s="9"/>
+      <c r="K156" s="9">
+        <v>0</v>
+      </c>
+      <c r="L156" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M156" s="8" t="s">
         <v>681</v>
       </c>
     </row>
-    <row r="157" s="4" customFormat="1" spans="1:13">
-      <c r="A157" s="11"/>
+    <row r="157" s="3" customFormat="1" spans="1:13">
+      <c r="A157" s="8"/>
       <c r="B157" s="1" t="s">
         <v>682</v>
       </c>
-      <c r="C157" s="11" t="s">
+      <c r="C157" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D157" s="12">
+      <c r="D157" s="9">
         <v>0.1</v>
       </c>
-      <c r="E157" s="11" t="s">
+      <c r="E157" s="8" t="s">
         <v>683</v>
       </c>
-      <c r="F157" s="11" t="s">
+      <c r="F157" s="8" t="s">
         <v>684</v>
       </c>
-      <c r="G157" s="12">
+      <c r="G157" s="9">
         <v>450</v>
       </c>
-      <c r="H157" s="12">
+      <c r="H157" s="9">
         <v>225</v>
       </c>
-      <c r="I157" s="12">
+      <c r="I157" s="9">
         <v>40043</v>
       </c>
-      <c r="J157" s="12"/>
-      <c r="K157" s="12">
-        <v>0</v>
-      </c>
-      <c r="L157" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M157" s="11" t="s">
+      <c r="J157" s="9"/>
+      <c r="K157" s="9">
+        <v>0</v>
+      </c>
+      <c r="L157" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M157" s="8" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="158" s="4" customFormat="1" spans="1:13">
-      <c r="A158" s="11"/>
+    <row r="158" s="3" customFormat="1" spans="1:13">
+      <c r="A158" s="8"/>
       <c r="B158" s="1" t="s">
         <v>686</v>
       </c>
-      <c r="C158" s="11" t="s">
+      <c r="C158" s="8" t="s">
         <v>520</v>
       </c>
-      <c r="D158" s="12">
+      <c r="D158" s="9">
         <v>0.1</v>
       </c>
-      <c r="E158" s="11" t="s">
+      <c r="E158" s="8" t="s">
         <v>687</v>
       </c>
-      <c r="F158" s="11" t="s">
+      <c r="F158" s="8" t="s">
         <v>688</v>
       </c>
-      <c r="G158" s="12">
+      <c r="G158" s="9">
         <v>450</v>
       </c>
-      <c r="H158" s="12">
+      <c r="H158" s="9">
         <v>225</v>
       </c>
-      <c r="I158" s="12">
+      <c r="I158" s="9">
         <v>40045</v>
       </c>
-      <c r="J158" s="12"/>
-      <c r="K158" s="12">
-        <v>0</v>
-      </c>
-      <c r="L158" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M158" s="11" t="s">
+      <c r="J158" s="9"/>
+      <c r="K158" s="9">
+        <v>0</v>
+      </c>
+      <c r="L158" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M158" s="8" t="s">
         <v>689</v>
       </c>
     </row>
